--- a/story_simulator/data/character_traits.xlsx
+++ b/story_simulator/data/character_traits.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="12840" yWindow="0" windowWidth="12760" windowHeight="16000" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="14100" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>Description</t>
   </si>
@@ -558,6 +558,78 @@
   </si>
   <si>
     <t>withdrawn</t>
+  </si>
+  <si>
+    <t>accessible</t>
+  </si>
+  <si>
+    <t>adaptable</t>
+  </si>
+  <si>
+    <t>adventurous</t>
+  </si>
+  <si>
+    <t>affable</t>
+  </si>
+  <si>
+    <t>affectionate</t>
+  </si>
+  <si>
+    <t>agreeable</t>
+  </si>
+  <si>
+    <t>ambitious</t>
+  </si>
+  <si>
+    <t>amicable</t>
+  </si>
+  <si>
+    <t>amusing</t>
+  </si>
+  <si>
+    <t>articulate</t>
+  </si>
+  <si>
+    <t>balanced</t>
+  </si>
+  <si>
+    <t>benevolent</t>
+  </si>
+  <si>
+    <t>brave</t>
+  </si>
+  <si>
+    <t>bright</t>
+  </si>
+  <si>
+    <t>brilliant</t>
+  </si>
+  <si>
+    <t>broad-minded</t>
+  </si>
+  <si>
+    <t>capable</t>
+  </si>
+  <si>
+    <t>captivating</t>
+  </si>
+  <si>
+    <t>careful</t>
+  </si>
+  <si>
+    <t>caring</t>
+  </si>
+  <si>
+    <t>charming</t>
+  </si>
+  <si>
+    <t>clear-headed</t>
+  </si>
+  <si>
+    <t>clever</t>
+  </si>
+  <si>
+    <t>compassionate</t>
   </si>
 </sst>
 </file>
@@ -878,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C175"/>
+  <dimension ref="A1:C199"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -2291,6 +2363,198 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B176" t="s">
+        <v>177</v>
+      </c>
+      <c r="C176" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B177" t="s">
+        <v>178</v>
+      </c>
+      <c r="C177" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B178" t="s">
+        <v>179</v>
+      </c>
+      <c r="C178" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B179" t="s">
+        <v>180</v>
+      </c>
+      <c r="C179" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B180" t="s">
+        <v>181</v>
+      </c>
+      <c r="C180" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B181" t="s">
+        <v>182</v>
+      </c>
+      <c r="C181" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B182" t="s">
+        <v>183</v>
+      </c>
+      <c r="C182" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B183" t="s">
+        <v>184</v>
+      </c>
+      <c r="C183" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B184" t="s">
+        <v>185</v>
+      </c>
+      <c r="C184" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B185" t="s">
+        <v>186</v>
+      </c>
+      <c r="C185" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B186" t="s">
+        <v>187</v>
+      </c>
+      <c r="C186" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B187" t="s">
+        <v>188</v>
+      </c>
+      <c r="C187" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B188" t="s">
+        <v>189</v>
+      </c>
+      <c r="C188" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B189" t="s">
+        <v>190</v>
+      </c>
+      <c r="C189" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B190" t="s">
+        <v>191</v>
+      </c>
+      <c r="C190" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B191" t="s">
+        <v>192</v>
+      </c>
+      <c r="C191" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B192" t="s">
+        <v>193</v>
+      </c>
+      <c r="C192" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B193" t="s">
+        <v>194</v>
+      </c>
+      <c r="C193" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B194" t="s">
+        <v>195</v>
+      </c>
+      <c r="C194" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B195" t="s">
+        <v>196</v>
+      </c>
+      <c r="C195" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B196" t="s">
+        <v>197</v>
+      </c>
+      <c r="C196" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B197" t="s">
+        <v>198</v>
+      </c>
+      <c r="C197" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B198" t="s">
+        <v>199</v>
+      </c>
+      <c r="C198" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B199" t="s">
+        <v>200</v>
+      </c>
+      <c r="C199" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/story_simulator/data/character_traits.xlsx
+++ b/story_simulator/data/character_traits.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t>Description</t>
   </si>
@@ -630,6 +630,57 @@
   </si>
   <si>
     <t>compassionate</t>
+  </si>
+  <si>
+    <t>confident</t>
+  </si>
+  <si>
+    <t>conscientous</t>
+  </si>
+  <si>
+    <t>considerate</t>
+  </si>
+  <si>
+    <t>courageous</t>
+  </si>
+  <si>
+    <t>courteous</t>
+  </si>
+  <si>
+    <t>creative</t>
+  </si>
+  <si>
+    <t>curious</t>
+  </si>
+  <si>
+    <t>daring</t>
+  </si>
+  <si>
+    <t>decent</t>
+  </si>
+  <si>
+    <t>decisive</t>
+  </si>
+  <si>
+    <t>educated</t>
+  </si>
+  <si>
+    <t>dependable</t>
+  </si>
+  <si>
+    <t>determined</t>
+  </si>
+  <si>
+    <t>dignified</t>
+  </si>
+  <si>
+    <t>diligent</t>
+  </si>
+  <si>
+    <t>diplomatic</t>
+  </si>
+  <si>
+    <t>disciplined</t>
   </si>
 </sst>
 </file>
@@ -950,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C199"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -2555,6 +2606,142 @@
         <v>1</v>
       </c>
     </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B200" t="s">
+        <v>201</v>
+      </c>
+      <c r="C200" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B201" t="s">
+        <v>202</v>
+      </c>
+      <c r="C201" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B202" t="s">
+        <v>203</v>
+      </c>
+      <c r="C202" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B203" t="s">
+        <v>204</v>
+      </c>
+      <c r="C203" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B204" t="s">
+        <v>205</v>
+      </c>
+      <c r="C204" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B205" t="s">
+        <v>206</v>
+      </c>
+      <c r="C205" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B206" t="s">
+        <v>207</v>
+      </c>
+      <c r="C206" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B207" t="s">
+        <v>208</v>
+      </c>
+      <c r="C207" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B208" t="s">
+        <v>209</v>
+      </c>
+      <c r="C208" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B209" t="s">
+        <v>210</v>
+      </c>
+      <c r="C209" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B210" t="s">
+        <v>211</v>
+      </c>
+      <c r="C210" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B211" t="s">
+        <v>212</v>
+      </c>
+      <c r="C211" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B212" t="s">
+        <v>213</v>
+      </c>
+      <c r="C212" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B213" t="s">
+        <v>214</v>
+      </c>
+      <c r="C213" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B214" t="s">
+        <v>215</v>
+      </c>
+      <c r="C214" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B215" t="s">
+        <v>216</v>
+      </c>
+      <c r="C215" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B216" t="s">
+        <v>217</v>
+      </c>
+      <c r="C216" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/story_simulator/data/character_traits.xlsx
+++ b/story_simulator/data/character_traits.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
   <si>
     <t>Description</t>
   </si>
@@ -681,6 +681,105 @@
   </si>
   <si>
     <t>disciplined</t>
+  </si>
+  <si>
+    <t>discreet</t>
+  </si>
+  <si>
+    <t>dynamic</t>
+  </si>
+  <si>
+    <t>easy-going</t>
+  </si>
+  <si>
+    <t>efficient</t>
+  </si>
+  <si>
+    <t>eloquent</t>
+  </si>
+  <si>
+    <t>empathetic</t>
+  </si>
+  <si>
+    <t>encouraging</t>
+  </si>
+  <si>
+    <t>energetic</t>
+  </si>
+  <si>
+    <t>enthusiastic</t>
+  </si>
+  <si>
+    <t>exuberant</t>
+  </si>
+  <si>
+    <t>fair</t>
+  </si>
+  <si>
+    <t>faithful</t>
+  </si>
+  <si>
+    <t>fearless</t>
+  </si>
+  <si>
+    <t>firm</t>
+  </si>
+  <si>
+    <t>flexible</t>
+  </si>
+  <si>
+    <t>focused</t>
+  </si>
+  <si>
+    <t>forgiving</t>
+  </si>
+  <si>
+    <t>frank</t>
+  </si>
+  <si>
+    <t>funny</t>
+  </si>
+  <si>
+    <t>generous</t>
+  </si>
+  <si>
+    <t>gentle</t>
+  </si>
+  <si>
+    <t>genuine</t>
+  </si>
+  <si>
+    <t>gracious</t>
+  </si>
+  <si>
+    <t>gregarious</t>
+  </si>
+  <si>
+    <t>hard-working</t>
+  </si>
+  <si>
+    <t>helpful</t>
+  </si>
+  <si>
+    <t>honest</t>
+  </si>
+  <si>
+    <t>humble</t>
+  </si>
+  <si>
+    <t>humorous</t>
+  </si>
+  <si>
+    <t>idealistic</t>
+  </si>
+  <si>
+    <t>imaginative</t>
+  </si>
+  <si>
+    <t>impartial</t>
+  </si>
+  <si>
+    <t>incisive</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C249"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -2688,7 +2787,7 @@
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B210" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C210" s="1">
         <v>1</v>
@@ -2696,7 +2795,7 @@
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B211" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C211" s="1">
         <v>1</v>
@@ -2704,23 +2803,23 @@
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B212" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C212" s="1">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B213" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C213" s="1">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B214" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C214" s="1">
         <v>1</v>
@@ -2728,7 +2827,7 @@
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B215" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C215" s="1">
         <v>1</v>
@@ -2736,9 +2835,273 @@
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B216" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C216" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B217" t="s">
+        <v>219</v>
+      </c>
+      <c r="C217" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B218" t="s">
+        <v>220</v>
+      </c>
+      <c r="C218" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B219" t="s">
+        <v>211</v>
+      </c>
+      <c r="C219" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B220" t="s">
+        <v>221</v>
+      </c>
+      <c r="C220" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B221" t="s">
+        <v>222</v>
+      </c>
+      <c r="C221" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B222" t="s">
+        <v>223</v>
+      </c>
+      <c r="C222" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B223" t="s">
+        <v>224</v>
+      </c>
+      <c r="C223" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B224" t="s">
+        <v>225</v>
+      </c>
+      <c r="C224" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B225" t="s">
+        <v>226</v>
+      </c>
+      <c r="C225" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B226" t="s">
+        <v>227</v>
+      </c>
+      <c r="C226" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B227" t="s">
+        <v>228</v>
+      </c>
+      <c r="C227" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B228" t="s">
+        <v>229</v>
+      </c>
+      <c r="C228" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B229" t="s">
+        <v>230</v>
+      </c>
+      <c r="C229" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B230" t="s">
+        <v>231</v>
+      </c>
+      <c r="C230" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B231" t="s">
+        <v>232</v>
+      </c>
+      <c r="C231" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B232" t="s">
+        <v>233</v>
+      </c>
+      <c r="C232" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B233" t="s">
+        <v>234</v>
+      </c>
+      <c r="C233" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B234" t="s">
+        <v>235</v>
+      </c>
+      <c r="C234" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B235" t="s">
+        <v>236</v>
+      </c>
+      <c r="C235" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B236" t="s">
+        <v>237</v>
+      </c>
+      <c r="C236" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B237" t="s">
+        <v>238</v>
+      </c>
+      <c r="C237" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B238" t="s">
+        <v>239</v>
+      </c>
+      <c r="C238" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B239" t="s">
+        <v>240</v>
+      </c>
+      <c r="C239" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B240" t="s">
+        <v>241</v>
+      </c>
+      <c r="C240" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B241" t="s">
+        <v>242</v>
+      </c>
+      <c r="C241" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B242" t="s">
+        <v>243</v>
+      </c>
+      <c r="C242" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B243" t="s">
+        <v>244</v>
+      </c>
+      <c r="C243" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B244" t="s">
+        <v>245</v>
+      </c>
+      <c r="C244" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B245" t="s">
+        <v>246</v>
+      </c>
+      <c r="C245" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B246" t="s">
+        <v>247</v>
+      </c>
+      <c r="C246" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B247" t="s">
+        <v>248</v>
+      </c>
+      <c r="C247" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B248" t="s">
+        <v>249</v>
+      </c>
+      <c r="C248" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B249" t="s">
+        <v>250</v>
+      </c>
+      <c r="C249" s="1">
         <v>1</v>
       </c>
     </row>

--- a/story_simulator/data/character_traits.xlsx
+++ b/story_simulator/data/character_traits.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="14100" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12760" windowHeight="16000" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
   <si>
     <t>Description</t>
   </si>
@@ -780,6 +780,282 @@
   </si>
   <si>
     <t>incisive</t>
+  </si>
+  <si>
+    <t>independent</t>
+  </si>
+  <si>
+    <t>innovative</t>
+  </si>
+  <si>
+    <t>insightful</t>
+  </si>
+  <si>
+    <t>intelligent</t>
+  </si>
+  <si>
+    <t>intuitive</t>
+  </si>
+  <si>
+    <t>inventive</t>
+  </si>
+  <si>
+    <t>keen</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>liberal</t>
+  </si>
+  <si>
+    <t>logical</t>
+  </si>
+  <si>
+    <t>loving</t>
+  </si>
+  <si>
+    <t>loyal</t>
+  </si>
+  <si>
+    <t>magnanimous</t>
+  </si>
+  <si>
+    <t>mature</t>
+  </si>
+  <si>
+    <t>meticulous</t>
+  </si>
+  <si>
+    <t>moderate</t>
+  </si>
+  <si>
+    <t>modest</t>
+  </si>
+  <si>
+    <t>neat</t>
+  </si>
+  <si>
+    <t>obedient</t>
+  </si>
+  <si>
+    <t>objective</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>optimistic</t>
+  </si>
+  <si>
+    <t>orderly</t>
+  </si>
+  <si>
+    <t>organized</t>
+  </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>passionate</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>peaceful</t>
+  </si>
+  <si>
+    <t>perceptive</t>
+  </si>
+  <si>
+    <t>persistent</t>
+  </si>
+  <si>
+    <t>personable</t>
+  </si>
+  <si>
+    <t>persuasive</t>
+  </si>
+  <si>
+    <t>pioneering</t>
+  </si>
+  <si>
+    <t>placid</t>
+  </si>
+  <si>
+    <t>plucky</t>
+  </si>
+  <si>
+    <t>polished</t>
+  </si>
+  <si>
+    <t>polite</t>
+  </si>
+  <si>
+    <t>practical</t>
+  </si>
+  <si>
+    <t>precise</t>
+  </si>
+  <si>
+    <t>principled</t>
+  </si>
+  <si>
+    <t>protective</t>
+  </si>
+  <si>
+    <t>prudent</t>
+  </si>
+  <si>
+    <t>punctual</t>
+  </si>
+  <si>
+    <t>quick-witted</t>
+  </si>
+  <si>
+    <t>quiet</t>
+  </si>
+  <si>
+    <t>rational</t>
+  </si>
+  <si>
+    <t>relaxed</t>
+  </si>
+  <si>
+    <t>reliable</t>
+  </si>
+  <si>
+    <t>reserved</t>
+  </si>
+  <si>
+    <t>resourceful</t>
+  </si>
+  <si>
+    <t>responsible</t>
+  </si>
+  <si>
+    <t>responsive</t>
+  </si>
+  <si>
+    <t>romantic</t>
+  </si>
+  <si>
+    <t>scrupulous</t>
+  </si>
+  <si>
+    <t>secure</t>
+  </si>
+  <si>
+    <t>self-confident</t>
+  </si>
+  <si>
+    <t>self-disciplined</t>
+  </si>
+  <si>
+    <t>selfless</t>
+  </si>
+  <si>
+    <t>sensible</t>
+  </si>
+  <si>
+    <t>sensitive</t>
+  </si>
+  <si>
+    <t>shy</t>
+  </si>
+  <si>
+    <t>sincere</t>
+  </si>
+  <si>
+    <t>skilful</t>
+  </si>
+  <si>
+    <t>sociable</t>
+  </si>
+  <si>
+    <t>spontaneous</t>
+  </si>
+  <si>
+    <t>sporting</t>
+  </si>
+  <si>
+    <t>stable</t>
+  </si>
+  <si>
+    <t>steadfast</t>
+  </si>
+  <si>
+    <t>stoic</t>
+  </si>
+  <si>
+    <t>straightforward</t>
+  </si>
+  <si>
+    <t>strong</t>
+  </si>
+  <si>
+    <t>suave</t>
+  </si>
+  <si>
+    <t>subtle</t>
+  </si>
+  <si>
+    <t>sympathetic</t>
+  </si>
+  <si>
+    <t>tasteful</t>
+  </si>
+  <si>
+    <t>thorough</t>
+  </si>
+  <si>
+    <t>thoughtful</t>
+  </si>
+  <si>
+    <t>tidy</t>
+  </si>
+  <si>
+    <t>tolerant</t>
+  </si>
+  <si>
+    <t>tough</t>
+  </si>
+  <si>
+    <t>unassuming</t>
+  </si>
+  <si>
+    <t>uncomplaining</t>
+  </si>
+  <si>
+    <t>understanding</t>
+  </si>
+  <si>
+    <t>upright</t>
+  </si>
+  <si>
+    <t>versatile</t>
+  </si>
+  <si>
+    <t>vivacious</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>well-read</t>
+  </si>
+  <si>
+    <t>well-rounded</t>
+  </si>
+  <si>
+    <t>willing</t>
+  </si>
+  <si>
+    <t>wise</t>
+  </si>
+  <si>
+    <t>witty</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C249"/>
+  <dimension ref="A1:C341"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -1130,6 +1406,9 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -1138,6 +1417,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -1146,6 +1428,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -1154,6 +1439,9 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -1162,6 +1450,9 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1170,6 +1461,9 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
@@ -1178,6 +1472,9 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -1186,6 +1483,9 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
@@ -1194,6 +1494,9 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1</v>
+      </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
@@ -1202,6 +1505,9 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1</v>
+      </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
@@ -1210,6 +1516,9 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
@@ -1218,6 +1527,9 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1226,6 +1538,9 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -1234,6 +1549,9 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1</v>
+      </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -1241,7 +1559,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1</v>
+      </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -1249,7 +1570,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -1257,7 +1581,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1</v>
+      </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1265,7 +1592,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>1</v>
+      </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
@@ -1273,7 +1603,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1</v>
+      </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
@@ -1281,7 +1614,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>1</v>
+      </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
@@ -1289,7 +1625,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>1</v>
+      </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
@@ -1297,7 +1636,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>1</v>
+      </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
@@ -1305,7 +1647,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>1</v>
+      </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
@@ -1313,7 +1658,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>1</v>
+      </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
@@ -1321,7 +1669,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>1</v>
+      </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
@@ -1329,7 +1680,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>1</v>
+      </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
@@ -1337,7 +1691,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1</v>
+      </c>
       <c r="B29" t="s">
         <v>30</v>
       </c>
@@ -1345,7 +1702,10 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>1</v>
+      </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>
@@ -1353,7 +1713,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>1</v>
+      </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
@@ -1361,7 +1724,10 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>1</v>
+      </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
@@ -1369,7 +1735,10 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>1</v>
+      </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
@@ -1377,7 +1746,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>1</v>
+      </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
@@ -1385,7 +1757,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>1</v>
+      </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
@@ -1393,7 +1768,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>1</v>
+      </c>
       <c r="B36" t="s">
         <v>37</v>
       </c>
@@ -1401,7 +1779,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>1</v>
+      </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
@@ -1409,7 +1790,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>1</v>
+      </c>
       <c r="B38" t="s">
         <v>39</v>
       </c>
@@ -1417,7 +1801,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>1</v>
+      </c>
       <c r="B39" t="s">
         <v>40</v>
       </c>
@@ -1425,7 +1812,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>1</v>
+      </c>
       <c r="B40" t="s">
         <v>41</v>
       </c>
@@ -1433,7 +1823,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>1</v>
+      </c>
       <c r="B41" t="s">
         <v>42</v>
       </c>
@@ -1441,7 +1834,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>1</v>
+      </c>
       <c r="B42" t="s">
         <v>43</v>
       </c>
@@ -1449,7 +1845,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>1</v>
+      </c>
       <c r="B43" t="s">
         <v>44</v>
       </c>
@@ -1457,7 +1856,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>1</v>
+      </c>
       <c r="B44" t="s">
         <v>45</v>
       </c>
@@ -1465,7 +1867,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>1</v>
+      </c>
       <c r="B45" t="s">
         <v>46</v>
       </c>
@@ -1473,7 +1878,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>1</v>
+      </c>
       <c r="B46" t="s">
         <v>47</v>
       </c>
@@ -1481,7 +1889,10 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>1</v>
+      </c>
       <c r="B47" t="s">
         <v>48</v>
       </c>
@@ -1489,7 +1900,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>1</v>
+      </c>
       <c r="B48" t="s">
         <v>49</v>
       </c>
@@ -1497,7 +1911,10 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>1</v>
+      </c>
       <c r="B49" t="s">
         <v>50</v>
       </c>
@@ -1505,7 +1922,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>1</v>
+      </c>
       <c r="B50" t="s">
         <v>51</v>
       </c>
@@ -1513,7 +1933,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>1</v>
+      </c>
       <c r="B51" t="s">
         <v>52</v>
       </c>
@@ -1521,7 +1944,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>1</v>
+      </c>
       <c r="B52" t="s">
         <v>53</v>
       </c>
@@ -1529,7 +1955,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>1</v>
+      </c>
       <c r="B53" t="s">
         <v>54</v>
       </c>
@@ -1537,7 +1966,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>1</v>
+      </c>
       <c r="B54" t="s">
         <v>55</v>
       </c>
@@ -1545,7 +1977,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>1</v>
+      </c>
       <c r="B55" t="s">
         <v>56</v>
       </c>
@@ -1553,7 +1988,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>1</v>
+      </c>
       <c r="B56" t="s">
         <v>57</v>
       </c>
@@ -1561,7 +1999,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>1</v>
+      </c>
       <c r="B57" t="s">
         <v>58</v>
       </c>
@@ -1569,7 +2010,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>1</v>
+      </c>
       <c r="B58" t="s">
         <v>59</v>
       </c>
@@ -1577,7 +2021,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>1</v>
+      </c>
       <c r="B59" t="s">
         <v>60</v>
       </c>
@@ -1585,7 +2032,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>1</v>
+      </c>
       <c r="B60" t="s">
         <v>61</v>
       </c>
@@ -1593,7 +2043,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>1</v>
+      </c>
       <c r="B61" t="s">
         <v>62</v>
       </c>
@@ -1601,7 +2054,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>1</v>
+      </c>
       <c r="B62" t="s">
         <v>63</v>
       </c>
@@ -1609,7 +2065,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>1</v>
+      </c>
       <c r="B63" t="s">
         <v>64</v>
       </c>
@@ -1617,7 +2076,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>1</v>
+      </c>
       <c r="B64" t="s">
         <v>65</v>
       </c>
@@ -1625,7 +2087,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>1</v>
+      </c>
       <c r="B65" t="s">
         <v>66</v>
       </c>
@@ -1633,7 +2098,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>1</v>
+      </c>
       <c r="B66" t="s">
         <v>67</v>
       </c>
@@ -1641,7 +2109,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>1</v>
+      </c>
       <c r="B67" t="s">
         <v>68</v>
       </c>
@@ -1649,7 +2120,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>1</v>
+      </c>
       <c r="B68" t="s">
         <v>69</v>
       </c>
@@ -1657,7 +2131,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>1</v>
+      </c>
       <c r="B69" t="s">
         <v>70</v>
       </c>
@@ -1665,7 +2142,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>1</v>
+      </c>
       <c r="B70" t="s">
         <v>71</v>
       </c>
@@ -1673,7 +2153,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>1</v>
+      </c>
       <c r="B71" t="s">
         <v>72</v>
       </c>
@@ -1681,7 +2164,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>1</v>
+      </c>
       <c r="B72" t="s">
         <v>73</v>
       </c>
@@ -1689,7 +2175,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>1</v>
+      </c>
       <c r="B73" t="s">
         <v>74</v>
       </c>
@@ -1697,7 +2186,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>1</v>
+      </c>
       <c r="B74" t="s">
         <v>75</v>
       </c>
@@ -1705,7 +2197,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>1</v>
+      </c>
       <c r="B75" t="s">
         <v>76</v>
       </c>
@@ -1713,7 +2208,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>1</v>
+      </c>
       <c r="B76" t="s">
         <v>77</v>
       </c>
@@ -1721,7 +2219,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>1</v>
+      </c>
       <c r="B77" t="s">
         <v>78</v>
       </c>
@@ -1729,7 +2230,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>1</v>
+      </c>
       <c r="B78" t="s">
         <v>79</v>
       </c>
@@ -1737,7 +2241,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>1</v>
+      </c>
       <c r="B79" t="s">
         <v>80</v>
       </c>
@@ -1745,7 +2252,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>1</v>
+      </c>
       <c r="B80" t="s">
         <v>81</v>
       </c>
@@ -1753,7 +2263,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>1</v>
+      </c>
       <c r="B81" t="s">
         <v>82</v>
       </c>
@@ -1761,7 +2274,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>1</v>
+      </c>
       <c r="B82" t="s">
         <v>83</v>
       </c>
@@ -1769,7 +2285,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>1</v>
+      </c>
       <c r="B83" t="s">
         <v>85</v>
       </c>
@@ -1777,7 +2296,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>1</v>
+      </c>
       <c r="B84" t="s">
         <v>84</v>
       </c>
@@ -1785,7 +2307,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>1</v>
+      </c>
       <c r="B85" t="s">
         <v>86</v>
       </c>
@@ -1793,7 +2318,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>1</v>
+      </c>
       <c r="B86" t="s">
         <v>87</v>
       </c>
@@ -1801,7 +2329,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>1</v>
+      </c>
       <c r="B87" t="s">
         <v>88</v>
       </c>
@@ -1809,7 +2340,10 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>1</v>
+      </c>
       <c r="B88" t="s">
         <v>89</v>
       </c>
@@ -1817,7 +2351,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>1</v>
+      </c>
       <c r="B89" t="s">
         <v>90</v>
       </c>
@@ -1825,7 +2362,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>1</v>
+      </c>
       <c r="B90" t="s">
         <v>91</v>
       </c>
@@ -1833,7 +2373,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>1</v>
+      </c>
       <c r="B91" t="s">
         <v>92</v>
       </c>
@@ -1841,7 +2384,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>1</v>
+      </c>
       <c r="B92" t="s">
         <v>93</v>
       </c>
@@ -1849,7 +2395,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>1</v>
+      </c>
       <c r="B93" t="s">
         <v>94</v>
       </c>
@@ -1857,7 +2406,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>1</v>
+      </c>
       <c r="B94" t="s">
         <v>95</v>
       </c>
@@ -1865,7 +2417,10 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>1</v>
+      </c>
       <c r="B95" t="s">
         <v>96</v>
       </c>
@@ -1873,7 +2428,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>1</v>
+      </c>
       <c r="B96" t="s">
         <v>97</v>
       </c>
@@ -1881,7 +2439,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>1</v>
+      </c>
       <c r="B97" t="s">
         <v>98</v>
       </c>
@@ -1889,7 +2450,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>1</v>
+      </c>
       <c r="B98" t="s">
         <v>99</v>
       </c>
@@ -1897,7 +2461,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>1</v>
+      </c>
       <c r="B99" t="s">
         <v>100</v>
       </c>
@@ -1905,7 +2472,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>1</v>
+      </c>
       <c r="B100" t="s">
         <v>101</v>
       </c>
@@ -1913,7 +2483,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>1</v>
+      </c>
       <c r="B101" t="s">
         <v>102</v>
       </c>
@@ -1921,7 +2494,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>1</v>
+      </c>
       <c r="B102" t="s">
         <v>103</v>
       </c>
@@ -1929,7 +2505,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>1</v>
+      </c>
       <c r="B103" t="s">
         <v>104</v>
       </c>
@@ -1937,7 +2516,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>1</v>
+      </c>
       <c r="B104" t="s">
         <v>105</v>
       </c>
@@ -1945,7 +2527,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>1</v>
+      </c>
       <c r="B105" t="s">
         <v>106</v>
       </c>
@@ -1953,7 +2538,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>1</v>
+      </c>
       <c r="B106" t="s">
         <v>107</v>
       </c>
@@ -1961,7 +2549,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>1</v>
+      </c>
       <c r="B107" t="s">
         <v>108</v>
       </c>
@@ -1969,7 +2560,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>1</v>
+      </c>
       <c r="B108" t="s">
         <v>109</v>
       </c>
@@ -1977,7 +2571,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>1</v>
+      </c>
       <c r="B109" t="s">
         <v>110</v>
       </c>
@@ -1985,7 +2582,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>1</v>
+      </c>
       <c r="B110" t="s">
         <v>111</v>
       </c>
@@ -1993,7 +2593,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>1</v>
+      </c>
       <c r="B111" t="s">
         <v>112</v>
       </c>
@@ -2001,7 +2604,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>1</v>
+      </c>
       <c r="B112" t="s">
         <v>113</v>
       </c>
@@ -2009,7 +2615,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>1</v>
+      </c>
       <c r="B113" t="s">
         <v>114</v>
       </c>
@@ -2017,7 +2626,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>1</v>
+      </c>
       <c r="B114" t="s">
         <v>115</v>
       </c>
@@ -2025,7 +2637,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>1</v>
+      </c>
       <c r="B115" t="s">
         <v>116</v>
       </c>
@@ -2033,7 +2648,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>1</v>
+      </c>
       <c r="B116" t="s">
         <v>117</v>
       </c>
@@ -2041,7 +2659,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>1</v>
+      </c>
       <c r="B117" t="s">
         <v>118</v>
       </c>
@@ -2049,7 +2670,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>1</v>
+      </c>
       <c r="B118" t="s">
         <v>119</v>
       </c>
@@ -2057,7 +2681,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>1</v>
+      </c>
       <c r="B119" t="s">
         <v>120</v>
       </c>
@@ -2065,7 +2692,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>1</v>
+      </c>
       <c r="B120" t="s">
         <v>121</v>
       </c>
@@ -2073,7 +2703,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>1</v>
+      </c>
       <c r="B121" t="s">
         <v>122</v>
       </c>
@@ -2081,7 +2714,10 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>1</v>
+      </c>
       <c r="B122" t="s">
         <v>123</v>
       </c>
@@ -2089,7 +2725,10 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>1</v>
+      </c>
       <c r="B123" t="s">
         <v>124</v>
       </c>
@@ -2097,7 +2736,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>1</v>
+      </c>
       <c r="B124" t="s">
         <v>125</v>
       </c>
@@ -2105,7 +2747,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>1</v>
+      </c>
       <c r="B125" t="s">
         <v>126</v>
       </c>
@@ -2113,7 +2758,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>1</v>
+      </c>
       <c r="B126" t="s">
         <v>127</v>
       </c>
@@ -2121,7 +2769,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>1</v>
+      </c>
       <c r="B127" t="s">
         <v>128</v>
       </c>
@@ -2129,7 +2780,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>1</v>
+      </c>
       <c r="B128" t="s">
         <v>129</v>
       </c>
@@ -2137,7 +2791,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>1</v>
+      </c>
       <c r="B129" t="s">
         <v>130</v>
       </c>
@@ -2145,7 +2802,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>1</v>
+      </c>
       <c r="B130" t="s">
         <v>131</v>
       </c>
@@ -2153,7 +2813,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>1</v>
+      </c>
       <c r="B131" t="s">
         <v>132</v>
       </c>
@@ -2161,7 +2824,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>1</v>
+      </c>
       <c r="B132" t="s">
         <v>133</v>
       </c>
@@ -2169,7 +2835,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>1</v>
+      </c>
       <c r="B133" t="s">
         <v>134</v>
       </c>
@@ -2177,7 +2846,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>1</v>
+      </c>
       <c r="B134" t="s">
         <v>135</v>
       </c>
@@ -2185,7 +2857,10 @@
         <v>-1.25</v>
       </c>
     </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>1</v>
+      </c>
       <c r="B135" t="s">
         <v>136</v>
       </c>
@@ -2193,7 +2868,10 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>1</v>
+      </c>
       <c r="B136" t="s">
         <v>137</v>
       </c>
@@ -2201,7 +2879,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>1</v>
+      </c>
       <c r="B137" t="s">
         <v>138</v>
       </c>
@@ -2209,7 +2890,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>1</v>
+      </c>
       <c r="B138" t="s">
         <v>139</v>
       </c>
@@ -2217,7 +2901,10 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>1</v>
+      </c>
       <c r="B139" t="s">
         <v>140</v>
       </c>
@@ -2225,7 +2912,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>1</v>
+      </c>
       <c r="B140" t="s">
         <v>141</v>
       </c>
@@ -2233,7 +2923,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>1</v>
+      </c>
       <c r="B141" t="s">
         <v>142</v>
       </c>
@@ -2241,7 +2934,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>1</v>
+      </c>
       <c r="B142" t="s">
         <v>143</v>
       </c>
@@ -2249,7 +2945,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>1</v>
+      </c>
       <c r="B143" t="s">
         <v>144</v>
       </c>
@@ -2257,7 +2956,10 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>1</v>
+      </c>
       <c r="B144" t="s">
         <v>145</v>
       </c>
@@ -2265,7 +2967,10 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>1</v>
+      </c>
       <c r="B145" t="s">
         <v>146</v>
       </c>
@@ -2273,7 +2978,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>1</v>
+      </c>
       <c r="B146" t="s">
         <v>147</v>
       </c>
@@ -2281,7 +2989,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>1</v>
+      </c>
       <c r="B147" t="s">
         <v>148</v>
       </c>
@@ -2289,7 +3000,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>1</v>
+      </c>
       <c r="B148" t="s">
         <v>149</v>
       </c>
@@ -2297,7 +3011,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>1</v>
+      </c>
       <c r="B149" t="s">
         <v>150</v>
       </c>
@@ -2305,7 +3022,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>1</v>
+      </c>
       <c r="B150" t="s">
         <v>151</v>
       </c>
@@ -2313,7 +3033,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>1</v>
+      </c>
       <c r="B151" t="s">
         <v>152</v>
       </c>
@@ -2321,7 +3044,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>1</v>
+      </c>
       <c r="B152" t="s">
         <v>153</v>
       </c>
@@ -2329,7 +3055,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>1</v>
+      </c>
       <c r="B153" t="s">
         <v>154</v>
       </c>
@@ -2337,7 +3066,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>1</v>
+      </c>
       <c r="B154" t="s">
         <v>155</v>
       </c>
@@ -2345,7 +3077,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>1</v>
+      </c>
       <c r="B155" t="s">
         <v>156</v>
       </c>
@@ -2353,7 +3088,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>1</v>
+      </c>
       <c r="B156" t="s">
         <v>157</v>
       </c>
@@ -2361,7 +3099,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>1</v>
+      </c>
       <c r="B157" t="s">
         <v>158</v>
       </c>
@@ -2369,7 +3110,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>1</v>
+      </c>
       <c r="B158" t="s">
         <v>159</v>
       </c>
@@ -2377,7 +3121,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>1</v>
+      </c>
       <c r="B159" t="s">
         <v>160</v>
       </c>
@@ -2385,7 +3132,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>1</v>
+      </c>
       <c r="B160" t="s">
         <v>161</v>
       </c>
@@ -2393,7 +3143,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>1</v>
+      </c>
       <c r="B161" t="s">
         <v>162</v>
       </c>
@@ -2401,7 +3154,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>1</v>
+      </c>
       <c r="B162" t="s">
         <v>163</v>
       </c>
@@ -2409,7 +3165,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>1</v>
+      </c>
       <c r="B163" t="s">
         <v>164</v>
       </c>
@@ -2417,7 +3176,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>1</v>
+      </c>
       <c r="B164" t="s">
         <v>165</v>
       </c>
@@ -2425,7 +3187,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>1</v>
+      </c>
       <c r="B165" t="s">
         <v>166</v>
       </c>
@@ -2433,7 +3198,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>1</v>
+      </c>
       <c r="B166" t="s">
         <v>167</v>
       </c>
@@ -2441,7 +3209,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>1</v>
+      </c>
       <c r="B167" t="s">
         <v>168</v>
       </c>
@@ -2449,7 +3220,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>1</v>
+      </c>
       <c r="B168" t="s">
         <v>169</v>
       </c>
@@ -2457,7 +3231,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>1</v>
+      </c>
       <c r="B169" t="s">
         <v>170</v>
       </c>
@@ -2465,7 +3242,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>1</v>
+      </c>
       <c r="B170" t="s">
         <v>171</v>
       </c>
@@ -2473,7 +3253,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>1</v>
+      </c>
       <c r="B171" t="s">
         <v>172</v>
       </c>
@@ -2481,7 +3264,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>1</v>
+      </c>
       <c r="B172" t="s">
         <v>173</v>
       </c>
@@ -2489,7 +3275,10 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>1</v>
+      </c>
       <c r="B173" t="s">
         <v>174</v>
       </c>
@@ -2497,7 +3286,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>1</v>
+      </c>
       <c r="B174" t="s">
         <v>175</v>
       </c>
@@ -2505,7 +3297,10 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>1</v>
+      </c>
       <c r="B175" t="s">
         <v>176</v>
       </c>
@@ -2513,7 +3308,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>1</v>
+      </c>
       <c r="B176" t="s">
         <v>177</v>
       </c>
@@ -2521,7 +3319,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>1</v>
+      </c>
       <c r="B177" t="s">
         <v>178</v>
       </c>
@@ -2529,7 +3330,10 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>1</v>
+      </c>
       <c r="B178" t="s">
         <v>179</v>
       </c>
@@ -2537,7 +3341,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>1</v>
+      </c>
       <c r="B179" t="s">
         <v>180</v>
       </c>
@@ -2545,7 +3352,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>1</v>
+      </c>
       <c r="B180" t="s">
         <v>181</v>
       </c>
@@ -2553,7 +3363,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>1</v>
+      </c>
       <c r="B181" t="s">
         <v>182</v>
       </c>
@@ -2561,7 +3374,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>1</v>
+      </c>
       <c r="B182" t="s">
         <v>183</v>
       </c>
@@ -2569,7 +3385,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>1</v>
+      </c>
       <c r="B183" t="s">
         <v>184</v>
       </c>
@@ -2577,7 +3396,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>1</v>
+      </c>
       <c r="B184" t="s">
         <v>185</v>
       </c>
@@ -2585,7 +3407,10 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>1</v>
+      </c>
       <c r="B185" t="s">
         <v>186</v>
       </c>
@@ -2593,7 +3418,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>1</v>
+      </c>
       <c r="B186" t="s">
         <v>187</v>
       </c>
@@ -2601,7 +3429,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>1</v>
+      </c>
       <c r="B187" t="s">
         <v>188</v>
       </c>
@@ -2609,7 +3440,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>1</v>
+      </c>
       <c r="B188" t="s">
         <v>189</v>
       </c>
@@ -2617,7 +3451,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>1</v>
+      </c>
       <c r="B189" t="s">
         <v>190</v>
       </c>
@@ -2625,7 +3462,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>1</v>
+      </c>
       <c r="B190" t="s">
         <v>191</v>
       </c>
@@ -2633,7 +3473,10 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>1</v>
+      </c>
       <c r="B191" t="s">
         <v>192</v>
       </c>
@@ -2641,7 +3484,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>1</v>
+      </c>
       <c r="B192" t="s">
         <v>193</v>
       </c>
@@ -2649,7 +3495,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>1</v>
+      </c>
       <c r="B193" t="s">
         <v>194</v>
       </c>
@@ -2657,7 +3506,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>1</v>
+      </c>
       <c r="B194" t="s">
         <v>195</v>
       </c>
@@ -2665,7 +3517,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>1</v>
+      </c>
       <c r="B195" t="s">
         <v>196</v>
       </c>
@@ -2673,7 +3528,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>1</v>
+      </c>
       <c r="B196" t="s">
         <v>197</v>
       </c>
@@ -2681,7 +3539,10 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>1</v>
+      </c>
       <c r="B197" t="s">
         <v>198</v>
       </c>
@@ -2689,7 +3550,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>1</v>
+      </c>
       <c r="B198" t="s">
         <v>199</v>
       </c>
@@ -2697,7 +3561,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>1</v>
+      </c>
       <c r="B199" t="s">
         <v>200</v>
       </c>
@@ -2705,7 +3572,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>1</v>
+      </c>
       <c r="B200" t="s">
         <v>201</v>
       </c>
@@ -2713,7 +3583,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>1</v>
+      </c>
       <c r="B201" t="s">
         <v>202</v>
       </c>
@@ -2721,7 +3594,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>1</v>
+      </c>
       <c r="B202" t="s">
         <v>203</v>
       </c>
@@ -2729,7 +3605,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>1</v>
+      </c>
       <c r="B203" t="s">
         <v>204</v>
       </c>
@@ -2737,7 +3616,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>1</v>
+      </c>
       <c r="B204" t="s">
         <v>205</v>
       </c>
@@ -2745,7 +3627,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>1</v>
+      </c>
       <c r="B205" t="s">
         <v>206</v>
       </c>
@@ -2753,7 +3638,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>1</v>
+      </c>
       <c r="B206" t="s">
         <v>207</v>
       </c>
@@ -2761,7 +3649,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>1</v>
+      </c>
       <c r="B207" t="s">
         <v>208</v>
       </c>
@@ -2769,7 +3660,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="208" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>1</v>
+      </c>
       <c r="B208" t="s">
         <v>209</v>
       </c>
@@ -2777,7 +3671,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>1</v>
+      </c>
       <c r="B209" t="s">
         <v>210</v>
       </c>
@@ -2785,7 +3682,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>1</v>
+      </c>
       <c r="B210" t="s">
         <v>212</v>
       </c>
@@ -2793,7 +3693,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>1</v>
+      </c>
       <c r="B211" t="s">
         <v>213</v>
       </c>
@@ -2801,7 +3704,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>1</v>
+      </c>
       <c r="B212" t="s">
         <v>214</v>
       </c>
@@ -2809,7 +3715,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>1</v>
+      </c>
       <c r="B213" t="s">
         <v>215</v>
       </c>
@@ -2817,7 +3726,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>1</v>
+      </c>
       <c r="B214" t="s">
         <v>216</v>
       </c>
@@ -2825,7 +3737,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>1</v>
+      </c>
       <c r="B215" t="s">
         <v>217</v>
       </c>
@@ -2833,7 +3748,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>1</v>
+      </c>
       <c r="B216" t="s">
         <v>218</v>
       </c>
@@ -2841,7 +3759,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>1</v>
+      </c>
       <c r="B217" t="s">
         <v>219</v>
       </c>
@@ -2849,7 +3770,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>1</v>
+      </c>
       <c r="B218" t="s">
         <v>220</v>
       </c>
@@ -2857,7 +3781,10 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>1</v>
+      </c>
       <c r="B219" t="s">
         <v>211</v>
       </c>
@@ -2865,7 +3792,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>1</v>
+      </c>
       <c r="B220" t="s">
         <v>221</v>
       </c>
@@ -2873,7 +3803,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>1</v>
+      </c>
       <c r="B221" t="s">
         <v>222</v>
       </c>
@@ -2881,7 +3814,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>1</v>
+      </c>
       <c r="B222" t="s">
         <v>223</v>
       </c>
@@ -2889,7 +3825,10 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>1</v>
+      </c>
       <c r="B223" t="s">
         <v>224</v>
       </c>
@@ -2897,7 +3836,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>1</v>
+      </c>
       <c r="B224" t="s">
         <v>225</v>
       </c>
@@ -2905,7 +3847,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="225" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>1</v>
+      </c>
       <c r="B225" t="s">
         <v>226</v>
       </c>
@@ -2913,7 +3858,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>1</v>
+      </c>
       <c r="B226" t="s">
         <v>227</v>
       </c>
@@ -2921,7 +3869,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>1</v>
+      </c>
       <c r="B227" t="s">
         <v>228</v>
       </c>
@@ -2929,7 +3880,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>1</v>
+      </c>
       <c r="B228" t="s">
         <v>229</v>
       </c>
@@ -2937,7 +3891,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>1</v>
+      </c>
       <c r="B229" t="s">
         <v>230</v>
       </c>
@@ -2945,7 +3902,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="230" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>1</v>
+      </c>
       <c r="B230" t="s">
         <v>231</v>
       </c>
@@ -2953,7 +3913,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>1</v>
+      </c>
       <c r="B231" t="s">
         <v>232</v>
       </c>
@@ -2961,7 +3924,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>1</v>
+      </c>
       <c r="B232" t="s">
         <v>233</v>
       </c>
@@ -2969,7 +3935,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>1</v>
+      </c>
       <c r="B233" t="s">
         <v>234</v>
       </c>
@@ -2977,7 +3946,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="234" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>1</v>
+      </c>
       <c r="B234" t="s">
         <v>235</v>
       </c>
@@ -2985,7 +3957,10 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="235" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>1</v>
+      </c>
       <c r="B235" t="s">
         <v>236</v>
       </c>
@@ -2993,7 +3968,10 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="236" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>1</v>
+      </c>
       <c r="B236" t="s">
         <v>237</v>
       </c>
@@ -3001,7 +3979,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="237" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>1</v>
+      </c>
       <c r="B237" t="s">
         <v>238</v>
       </c>
@@ -3009,7 +3990,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>1</v>
+      </c>
       <c r="B238" t="s">
         <v>239</v>
       </c>
@@ -3017,7 +4001,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>1</v>
+      </c>
       <c r="B239" t="s">
         <v>240</v>
       </c>
@@ -3025,7 +4012,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>1</v>
+      </c>
       <c r="B240" t="s">
         <v>241</v>
       </c>
@@ -3033,7 +4023,10 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="241" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>1</v>
+      </c>
       <c r="B241" t="s">
         <v>242</v>
       </c>
@@ -3041,7 +4034,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>1</v>
+      </c>
       <c r="B242" t="s">
         <v>243</v>
       </c>
@@ -3049,7 +4045,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>1</v>
+      </c>
       <c r="B243" t="s">
         <v>244</v>
       </c>
@@ -3057,7 +4056,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>1</v>
+      </c>
       <c r="B244" t="s">
         <v>245</v>
       </c>
@@ -3065,7 +4067,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>1</v>
+      </c>
       <c r="B245" t="s">
         <v>246</v>
       </c>
@@ -3073,7 +4078,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="246" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A246">
+        <v>1</v>
+      </c>
       <c r="B246" t="s">
         <v>247</v>
       </c>
@@ -3081,7 +4089,10 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="247" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A247">
+        <v>1</v>
+      </c>
       <c r="B247" t="s">
         <v>248</v>
       </c>
@@ -3089,7 +4100,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>1</v>
+      </c>
       <c r="B248" t="s">
         <v>249</v>
       </c>
@@ -3097,11 +4111,1026 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>1</v>
+      </c>
       <c r="B249" t="s">
         <v>250</v>
       </c>
       <c r="C249" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>1</v>
+      </c>
+      <c r="B250" t="s">
+        <v>251</v>
+      </c>
+      <c r="C250" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>1</v>
+      </c>
+      <c r="B251" t="s">
+        <v>252</v>
+      </c>
+      <c r="C251" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>1</v>
+      </c>
+      <c r="B252" t="s">
+        <v>253</v>
+      </c>
+      <c r="C252" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>1</v>
+      </c>
+      <c r="B253" t="s">
+        <v>254</v>
+      </c>
+      <c r="C253" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>1</v>
+      </c>
+      <c r="B254" t="s">
+        <v>255</v>
+      </c>
+      <c r="C254" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>1</v>
+      </c>
+      <c r="B255" t="s">
+        <v>256</v>
+      </c>
+      <c r="C255" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>1</v>
+      </c>
+      <c r="B256" t="s">
+        <v>257</v>
+      </c>
+      <c r="C256" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>1</v>
+      </c>
+      <c r="B257" t="s">
+        <v>258</v>
+      </c>
+      <c r="C257" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>1</v>
+      </c>
+      <c r="B258" t="s">
+        <v>259</v>
+      </c>
+      <c r="C258" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>1</v>
+      </c>
+      <c r="B259" t="s">
+        <v>260</v>
+      </c>
+      <c r="C259" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>1</v>
+      </c>
+      <c r="B260" t="s">
+        <v>261</v>
+      </c>
+      <c r="C260" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>1</v>
+      </c>
+      <c r="B261" t="s">
+        <v>262</v>
+      </c>
+      <c r="C261" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>1</v>
+      </c>
+      <c r="B262" t="s">
+        <v>263</v>
+      </c>
+      <c r="C262" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>1</v>
+      </c>
+      <c r="B263" t="s">
+        <v>264</v>
+      </c>
+      <c r="C263" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>1</v>
+      </c>
+      <c r="B264" t="s">
+        <v>265</v>
+      </c>
+      <c r="C264" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>1</v>
+      </c>
+      <c r="B265" t="s">
+        <v>266</v>
+      </c>
+      <c r="C265" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>1</v>
+      </c>
+      <c r="B266" t="s">
+        <v>267</v>
+      </c>
+      <c r="C266" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>1</v>
+      </c>
+      <c r="B267" t="s">
+        <v>268</v>
+      </c>
+      <c r="C267" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>1</v>
+      </c>
+      <c r="B268" t="s">
+        <v>269</v>
+      </c>
+      <c r="C268" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>1</v>
+      </c>
+      <c r="B269" t="s">
+        <v>270</v>
+      </c>
+      <c r="C269" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>1</v>
+      </c>
+      <c r="B270" t="s">
+        <v>271</v>
+      </c>
+      <c r="C270" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>1</v>
+      </c>
+      <c r="B271" t="s">
+        <v>272</v>
+      </c>
+      <c r="C271" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>1</v>
+      </c>
+      <c r="B272" t="s">
+        <v>273</v>
+      </c>
+      <c r="C272" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>1</v>
+      </c>
+      <c r="B273" t="s">
+        <v>274</v>
+      </c>
+      <c r="C273" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>1</v>
+      </c>
+      <c r="B274" t="s">
+        <v>275</v>
+      </c>
+      <c r="C274" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>1</v>
+      </c>
+      <c r="B275" t="s">
+        <v>276</v>
+      </c>
+      <c r="C275" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>1</v>
+      </c>
+      <c r="B276" t="s">
+        <v>277</v>
+      </c>
+      <c r="C276" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>1</v>
+      </c>
+      <c r="B277" t="s">
+        <v>278</v>
+      </c>
+      <c r="C277" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>1</v>
+      </c>
+      <c r="B278" t="s">
+        <v>279</v>
+      </c>
+      <c r="C278" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>1</v>
+      </c>
+      <c r="B279" t="s">
+        <v>280</v>
+      </c>
+      <c r="C279" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>1</v>
+      </c>
+      <c r="B280" t="s">
+        <v>281</v>
+      </c>
+      <c r="C280" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>1</v>
+      </c>
+      <c r="B281" t="s">
+        <v>282</v>
+      </c>
+      <c r="C281" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>1</v>
+      </c>
+      <c r="B282" t="s">
+        <v>283</v>
+      </c>
+      <c r="C282" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>1</v>
+      </c>
+      <c r="B283" t="s">
+        <v>284</v>
+      </c>
+      <c r="C283" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>1</v>
+      </c>
+      <c r="B284" t="s">
+        <v>285</v>
+      </c>
+      <c r="C284" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>1</v>
+      </c>
+      <c r="B285" t="s">
+        <v>286</v>
+      </c>
+      <c r="C285" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>1</v>
+      </c>
+      <c r="B286" t="s">
+        <v>287</v>
+      </c>
+      <c r="C286" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>1</v>
+      </c>
+      <c r="B287" t="s">
+        <v>288</v>
+      </c>
+      <c r="C287" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>1</v>
+      </c>
+      <c r="B288" t="s">
+        <v>289</v>
+      </c>
+      <c r="C288" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>1</v>
+      </c>
+      <c r="B289" t="s">
+        <v>290</v>
+      </c>
+      <c r="C289" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>1</v>
+      </c>
+      <c r="B290" t="s">
+        <v>291</v>
+      </c>
+      <c r="C290" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>1</v>
+      </c>
+      <c r="B291" t="s">
+        <v>292</v>
+      </c>
+      <c r="C291" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>1</v>
+      </c>
+      <c r="B292" t="s">
+        <v>293</v>
+      </c>
+      <c r="C292" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>1</v>
+      </c>
+      <c r="B293" t="s">
+        <v>294</v>
+      </c>
+      <c r="C293" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>1</v>
+      </c>
+      <c r="B294" t="s">
+        <v>295</v>
+      </c>
+      <c r="C294" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>1</v>
+      </c>
+      <c r="B295" t="s">
+        <v>296</v>
+      </c>
+      <c r="C295" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>1</v>
+      </c>
+      <c r="B296" t="s">
+        <v>297</v>
+      </c>
+      <c r="C296" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>1</v>
+      </c>
+      <c r="B297" t="s">
+        <v>298</v>
+      </c>
+      <c r="C297" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>1</v>
+      </c>
+      <c r="B298" t="s">
+        <v>299</v>
+      </c>
+      <c r="C298" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>1</v>
+      </c>
+      <c r="B299" t="s">
+        <v>300</v>
+      </c>
+      <c r="C299" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>1</v>
+      </c>
+      <c r="B300" t="s">
+        <v>301</v>
+      </c>
+      <c r="C300" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>1</v>
+      </c>
+      <c r="B301" t="s">
+        <v>302</v>
+      </c>
+      <c r="C301" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>1</v>
+      </c>
+      <c r="B302" t="s">
+        <v>303</v>
+      </c>
+      <c r="C302" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>1</v>
+      </c>
+      <c r="B303" t="s">
+        <v>304</v>
+      </c>
+      <c r="C303" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>1</v>
+      </c>
+      <c r="B304" t="s">
+        <v>305</v>
+      </c>
+      <c r="C304" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>1</v>
+      </c>
+      <c r="B305" t="s">
+        <v>306</v>
+      </c>
+      <c r="C305" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>1</v>
+      </c>
+      <c r="B306" t="s">
+        <v>307</v>
+      </c>
+      <c r="C306" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>1</v>
+      </c>
+      <c r="B307" t="s">
+        <v>308</v>
+      </c>
+      <c r="C307" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>1</v>
+      </c>
+      <c r="B308" t="s">
+        <v>309</v>
+      </c>
+      <c r="C308" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>1</v>
+      </c>
+      <c r="B309" t="s">
+        <v>310</v>
+      </c>
+      <c r="C309" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>1</v>
+      </c>
+      <c r="B310" t="s">
+        <v>311</v>
+      </c>
+      <c r="C310" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>1</v>
+      </c>
+      <c r="B311" t="s">
+        <v>312</v>
+      </c>
+      <c r="C311" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>1</v>
+      </c>
+      <c r="B312" t="s">
+        <v>313</v>
+      </c>
+      <c r="C312" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>1</v>
+      </c>
+      <c r="B313" t="s">
+        <v>314</v>
+      </c>
+      <c r="C313" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>1</v>
+      </c>
+      <c r="B314" t="s">
+        <v>315</v>
+      </c>
+      <c r="C314" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>1</v>
+      </c>
+      <c r="B315" t="s">
+        <v>316</v>
+      </c>
+      <c r="C315" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>1</v>
+      </c>
+      <c r="B316" t="s">
+        <v>317</v>
+      </c>
+      <c r="C316" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>1</v>
+      </c>
+      <c r="B317" t="s">
+        <v>318</v>
+      </c>
+      <c r="C317" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>1</v>
+      </c>
+      <c r="B318" t="s">
+        <v>319</v>
+      </c>
+      <c r="C318" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>1</v>
+      </c>
+      <c r="B319" t="s">
+        <v>320</v>
+      </c>
+      <c r="C319" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>1</v>
+      </c>
+      <c r="B320" t="s">
+        <v>321</v>
+      </c>
+      <c r="C320" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>1</v>
+      </c>
+      <c r="B321" t="s">
+        <v>322</v>
+      </c>
+      <c r="C321" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>1</v>
+      </c>
+      <c r="B322" t="s">
+        <v>323</v>
+      </c>
+      <c r="C322" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>1</v>
+      </c>
+      <c r="B323" t="s">
+        <v>324</v>
+      </c>
+      <c r="C323" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>1</v>
+      </c>
+      <c r="B324" t="s">
+        <v>325</v>
+      </c>
+      <c r="C324" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>1</v>
+      </c>
+      <c r="B325" t="s">
+        <v>326</v>
+      </c>
+      <c r="C325" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>1</v>
+      </c>
+      <c r="B326" t="s">
+        <v>327</v>
+      </c>
+      <c r="C326" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>1</v>
+      </c>
+      <c r="B327" t="s">
+        <v>328</v>
+      </c>
+      <c r="C327" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>1</v>
+      </c>
+      <c r="B328" t="s">
+        <v>329</v>
+      </c>
+      <c r="C328" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>1</v>
+      </c>
+      <c r="B329" t="s">
+        <v>330</v>
+      </c>
+      <c r="C329" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>1</v>
+      </c>
+      <c r="B330" t="s">
+        <v>331</v>
+      </c>
+      <c r="C330" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>1</v>
+      </c>
+      <c r="B331" t="s">
+        <v>332</v>
+      </c>
+      <c r="C331" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>1</v>
+      </c>
+      <c r="B332" t="s">
+        <v>333</v>
+      </c>
+      <c r="C332" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>1</v>
+      </c>
+      <c r="B333" t="s">
+        <v>334</v>
+      </c>
+      <c r="C333" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>1</v>
+      </c>
+      <c r="B334" t="s">
+        <v>335</v>
+      </c>
+      <c r="C334" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>1</v>
+      </c>
+      <c r="B335" t="s">
+        <v>336</v>
+      </c>
+      <c r="C335" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>1</v>
+      </c>
+      <c r="B336" t="s">
+        <v>337</v>
+      </c>
+      <c r="C336" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>1</v>
+      </c>
+      <c r="B337" t="s">
+        <v>338</v>
+      </c>
+      <c r="C337" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>1</v>
+      </c>
+      <c r="B338" t="s">
+        <v>339</v>
+      </c>
+      <c r="C338" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>1</v>
+      </c>
+      <c r="B339" t="s">
+        <v>340</v>
+      </c>
+      <c r="C339" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>1</v>
+      </c>
+      <c r="B340" t="s">
+        <v>341</v>
+      </c>
+      <c r="C340" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>1</v>
+      </c>
+      <c r="B341" t="s">
+        <v>342</v>
+      </c>
+      <c r="C341" s="1">
         <v>1</v>
       </c>
     </row>

--- a/story_simulator/data/character_traits.xlsx
+++ b/story_simulator/data/character_traits.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12760" windowHeight="16000" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="12760" windowHeight="14100" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
   <si>
     <t>Description</t>
   </si>
@@ -386,9 +386,6 @@
     <t>petulant</t>
   </si>
   <si>
-    <t>pick</t>
-  </si>
-  <si>
     <t>plodding</t>
   </si>
   <si>
@@ -1056,6 +1053,12 @@
   </si>
   <si>
     <t>witty</t>
+  </si>
+  <si>
+    <t>picky</t>
+  </si>
+  <si>
+    <t>Strength</t>
   </si>
 </sst>
 </file>
@@ -1376,14 +1379,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C341"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="49.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1393,8 +1396,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1404,8 +1410,11 @@
       <c r="C2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1415,8 +1424,11 @@
       <c r="C3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1426,8 +1438,11 @@
       <c r="C4">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1437,8 +1452,11 @@
       <c r="C5">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1448,8 +1466,11 @@
       <c r="C6">
         <v>-1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1459,8 +1480,11 @@
       <c r="C7">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1470,8 +1494,11 @@
       <c r="C8">
         <v>-1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1481,8 +1508,11 @@
       <c r="C9" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1492,8 +1522,11 @@
       <c r="C10">
         <v>-1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1503,8 +1536,11 @@
       <c r="C11" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1514,8 +1550,11 @@
       <c r="C12" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1525,8 +1564,11 @@
       <c r="C13" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1536,8 +1578,11 @@
       <c r="C14" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
@@ -1547,8 +1592,11 @@
       <c r="C15" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1558,8 +1606,11 @@
       <c r="C16" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1569,8 +1620,11 @@
       <c r="C17" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1580,8 +1634,11 @@
       <c r="C18" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1591,8 +1648,11 @@
       <c r="C19" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1602,8 +1662,11 @@
       <c r="C20" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1</v>
       </c>
@@ -1613,8 +1676,11 @@
       <c r="C21" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1</v>
       </c>
@@ -1624,8 +1690,11 @@
       <c r="C22" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1</v>
       </c>
@@ -1635,8 +1704,11 @@
       <c r="C23" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1</v>
       </c>
@@ -1646,8 +1718,11 @@
       <c r="C24" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1</v>
       </c>
@@ -1657,8 +1732,11 @@
       <c r="C25" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1</v>
       </c>
@@ -1668,8 +1746,11 @@
       <c r="C26" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1</v>
       </c>
@@ -1679,8 +1760,11 @@
       <c r="C27" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1</v>
       </c>
@@ -1690,8 +1774,11 @@
       <c r="C28" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1</v>
       </c>
@@ -1701,8 +1788,11 @@
       <c r="C29" s="1">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1712,8 +1802,11 @@
       <c r="C30" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1</v>
       </c>
@@ -1723,8 +1816,11 @@
       <c r="C31" s="1">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1</v>
       </c>
@@ -1734,8 +1830,11 @@
       <c r="C32" s="1">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1</v>
       </c>
@@ -1745,8 +1844,11 @@
       <c r="C33" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -1756,8 +1858,11 @@
       <c r="C34" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1</v>
       </c>
@@ -1767,8 +1872,11 @@
       <c r="C35" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1</v>
       </c>
@@ -1778,8 +1886,11 @@
       <c r="C36" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1</v>
       </c>
@@ -1789,8 +1900,11 @@
       <c r="C37" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1</v>
       </c>
@@ -1800,8 +1914,11 @@
       <c r="C38" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1</v>
       </c>
@@ -1811,8 +1928,11 @@
       <c r="C39" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1822,8 +1942,11 @@
       <c r="C40" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1</v>
       </c>
@@ -1833,8 +1956,11 @@
       <c r="C41" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1844,8 +1970,11 @@
       <c r="C42" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1</v>
       </c>
@@ -1855,8 +1984,11 @@
       <c r="C43" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1</v>
       </c>
@@ -1866,8 +1998,11 @@
       <c r="C44" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1</v>
       </c>
@@ -1877,8 +2012,11 @@
       <c r="C45" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1</v>
       </c>
@@ -1888,8 +2026,11 @@
       <c r="C46" s="1">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -1899,8 +2040,11 @@
       <c r="C47" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1</v>
       </c>
@@ -1910,8 +2054,11 @@
       <c r="C48" s="1">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1</v>
       </c>
@@ -1921,8 +2068,11 @@
       <c r="C49" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1</v>
       </c>
@@ -1932,8 +2082,11 @@
       <c r="C50" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1</v>
       </c>
@@ -1943,8 +2096,11 @@
       <c r="C51" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>1</v>
       </c>
@@ -1954,8 +2110,11 @@
       <c r="C52" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>1</v>
       </c>
@@ -1965,8 +2124,11 @@
       <c r="C53" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1</v>
       </c>
@@ -1976,8 +2138,11 @@
       <c r="C54" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1</v>
       </c>
@@ -1987,8 +2152,11 @@
       <c r="C55" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1</v>
       </c>
@@ -1998,8 +2166,11 @@
       <c r="C56" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1</v>
       </c>
@@ -2009,8 +2180,11 @@
       <c r="C57" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1</v>
       </c>
@@ -2020,8 +2194,11 @@
       <c r="C58" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1</v>
       </c>
@@ -2031,8 +2208,11 @@
       <c r="C59" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1</v>
       </c>
@@ -2042,8 +2222,11 @@
       <c r="C60" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>1</v>
       </c>
@@ -2053,8 +2236,11 @@
       <c r="C61" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>1</v>
       </c>
@@ -2064,8 +2250,11 @@
       <c r="C62" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>1</v>
       </c>
@@ -2075,8 +2264,11 @@
       <c r="C63" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>1</v>
       </c>
@@ -2086,8 +2278,11 @@
       <c r="C64" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>1</v>
       </c>
@@ -2097,8 +2292,11 @@
       <c r="C65" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -2108,8 +2306,11 @@
       <c r="C66" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>1</v>
       </c>
@@ -2119,8 +2320,11 @@
       <c r="C67" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>1</v>
       </c>
@@ -2130,8 +2334,11 @@
       <c r="C68" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>1</v>
       </c>
@@ -2141,8 +2348,11 @@
       <c r="C69" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>1</v>
       </c>
@@ -2152,8 +2362,11 @@
       <c r="C70" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>1</v>
       </c>
@@ -2163,8 +2376,11 @@
       <c r="C71" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>1</v>
       </c>
@@ -2174,8 +2390,11 @@
       <c r="C72" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>1</v>
       </c>
@@ -2185,8 +2404,11 @@
       <c r="C73" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>1</v>
       </c>
@@ -2196,8 +2418,11 @@
       <c r="C74" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>1</v>
       </c>
@@ -2207,8 +2432,11 @@
       <c r="C75" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>1</v>
       </c>
@@ -2218,8 +2446,11 @@
       <c r="C76" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>1</v>
       </c>
@@ -2229,8 +2460,11 @@
       <c r="C77" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>1</v>
       </c>
@@ -2240,8 +2474,11 @@
       <c r="C78" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>1</v>
       </c>
@@ -2251,8 +2488,11 @@
       <c r="C79" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>1</v>
       </c>
@@ -2262,8 +2502,11 @@
       <c r="C80" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>1</v>
       </c>
@@ -2273,8 +2516,11 @@
       <c r="C81" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>1</v>
       </c>
@@ -2284,8 +2530,11 @@
       <c r="C82" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>1</v>
       </c>
@@ -2295,8 +2544,11 @@
       <c r="C83" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>1</v>
       </c>
@@ -2306,8 +2558,11 @@
       <c r="C84" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>1</v>
       </c>
@@ -2317,8 +2572,11 @@
       <c r="C85" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>1</v>
       </c>
@@ -2328,8 +2586,11 @@
       <c r="C86" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>1</v>
       </c>
@@ -2339,8 +2600,11 @@
       <c r="C87" s="1">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>1</v>
       </c>
@@ -2350,8 +2614,11 @@
       <c r="C88" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>1</v>
       </c>
@@ -2361,8 +2628,11 @@
       <c r="C89" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>1</v>
       </c>
@@ -2372,8 +2642,11 @@
       <c r="C90" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>1</v>
       </c>
@@ -2383,8 +2656,11 @@
       <c r="C91" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>1</v>
       </c>
@@ -2394,8 +2670,11 @@
       <c r="C92" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>1</v>
       </c>
@@ -2405,8 +2684,11 @@
       <c r="C93" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>1</v>
       </c>
@@ -2416,8 +2698,11 @@
       <c r="C94" s="1">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>1</v>
       </c>
@@ -2427,8 +2712,11 @@
       <c r="C95" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>1</v>
       </c>
@@ -2438,8 +2726,11 @@
       <c r="C96" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>1</v>
       </c>
@@ -2449,8 +2740,11 @@
       <c r="C97" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -2460,8 +2754,11 @@
       <c r="C98" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>1</v>
       </c>
@@ -2471,8 +2768,11 @@
       <c r="C99" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>1</v>
       </c>
@@ -2482,8 +2782,11 @@
       <c r="C100" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>1</v>
       </c>
@@ -2493,8 +2796,11 @@
       <c r="C101" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>1</v>
       </c>
@@ -2504,8 +2810,11 @@
       <c r="C102" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>1</v>
       </c>
@@ -2515,8 +2824,11 @@
       <c r="C103" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>1</v>
       </c>
@@ -2526,8 +2838,11 @@
       <c r="C104" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>1</v>
       </c>
@@ -2537,8 +2852,11 @@
       <c r="C105" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>1</v>
       </c>
@@ -2548,8 +2866,11 @@
       <c r="C106" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>1</v>
       </c>
@@ -2559,8 +2880,11 @@
       <c r="C107" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>1</v>
       </c>
@@ -2570,8 +2894,11 @@
       <c r="C108" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>1</v>
       </c>
@@ -2581,8 +2908,11 @@
       <c r="C109" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>1</v>
       </c>
@@ -2592,8 +2922,11 @@
       <c r="C110" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>1</v>
       </c>
@@ -2603,8 +2936,11 @@
       <c r="C111" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>1</v>
       </c>
@@ -2614,8 +2950,11 @@
       <c r="C112" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>1</v>
       </c>
@@ -2625,8 +2964,11 @@
       <c r="C113" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>1</v>
       </c>
@@ -2636,8 +2978,11 @@
       <c r="C114" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>1</v>
       </c>
@@ -2647,8 +2992,11 @@
       <c r="C115" s="1">
         <v>-1</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>1</v>
       </c>
@@ -2658,8 +3006,11 @@
       <c r="C116" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>1</v>
       </c>
@@ -2669,2468 +3020,3143 @@
       <c r="C117" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>119</v>
+        <v>342</v>
       </c>
       <c r="C118" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C119" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>1</v>
       </c>
       <c r="B120" t="s">
+        <v>120</v>
+      </c>
+      <c r="C120" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>1</v>
+      </c>
+      <c r="B121" t="s">
         <v>121</v>
-      </c>
-      <c r="C120" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>1</v>
-      </c>
-      <c r="B121" t="s">
-        <v>122</v>
       </c>
       <c r="C121" s="1">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C122" s="1">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>1</v>
       </c>
       <c r="B123" t="s">
+        <v>123</v>
+      </c>
+      <c r="C123" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>1</v>
+      </c>
+      <c r="B124" t="s">
         <v>124</v>
-      </c>
-      <c r="C123" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>1</v>
-      </c>
-      <c r="B124" t="s">
-        <v>125</v>
       </c>
       <c r="C124" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C125" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C126" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C127" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C128" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>1</v>
       </c>
       <c r="B129" t="s">
+        <v>129</v>
+      </c>
+      <c r="C129" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>1</v>
+      </c>
+      <c r="B130" t="s">
         <v>130</v>
       </c>
-      <c r="C129" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>1</v>
-      </c>
-      <c r="B130" t="s">
+      <c r="C130" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>1</v>
+      </c>
+      <c r="B131" t="s">
         <v>131</v>
-      </c>
-      <c r="C130" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>1</v>
-      </c>
-      <c r="B131" t="s">
-        <v>132</v>
       </c>
       <c r="C131" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C132" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C133" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C134" s="1">
         <v>-1.25</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>1</v>
       </c>
       <c r="B135" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C135" s="1">
         <v>-1.5</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>1</v>
       </c>
       <c r="B136" t="s">
+        <v>136</v>
+      </c>
+      <c r="C136" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>1</v>
+      </c>
+      <c r="B137" t="s">
         <v>137</v>
-      </c>
-      <c r="C136" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>1</v>
-      </c>
-      <c r="B137" t="s">
-        <v>138</v>
       </c>
       <c r="C137" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C138" s="1">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>1</v>
       </c>
       <c r="B139" t="s">
+        <v>139</v>
+      </c>
+      <c r="C139" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>1</v>
+      </c>
+      <c r="B140" t="s">
         <v>140</v>
       </c>
-      <c r="C139" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>1</v>
-      </c>
-      <c r="B140" t="s">
+      <c r="C140" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>1</v>
+      </c>
+      <c r="B141" t="s">
         <v>141</v>
-      </c>
-      <c r="C140" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>1</v>
-      </c>
-      <c r="B141" t="s">
-        <v>142</v>
       </c>
       <c r="C141" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>1</v>
       </c>
       <c r="B142" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C142" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C143" s="1">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>1</v>
       </c>
       <c r="B144" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C144" s="1">
         <v>-0.25</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>1</v>
       </c>
       <c r="B145" t="s">
+        <v>145</v>
+      </c>
+      <c r="C145" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>1</v>
+      </c>
+      <c r="B146" t="s">
         <v>146</v>
-      </c>
-      <c r="C145" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>1</v>
-      </c>
-      <c r="B146" t="s">
-        <v>147</v>
       </c>
       <c r="C146" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>1</v>
       </c>
       <c r="B147" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C147" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>1</v>
       </c>
       <c r="B148" t="s">
+        <v>148</v>
+      </c>
+      <c r="C148" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>1</v>
+      </c>
+      <c r="B149" t="s">
         <v>149</v>
       </c>
-      <c r="C148" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>1</v>
-      </c>
-      <c r="B149" t="s">
+      <c r="C149" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>1</v>
+      </c>
+      <c r="B150" t="s">
         <v>150</v>
-      </c>
-      <c r="C149" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>1</v>
-      </c>
-      <c r="B150" t="s">
-        <v>151</v>
       </c>
       <c r="C150" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>1</v>
       </c>
       <c r="B151" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C151" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>1</v>
       </c>
       <c r="B152" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C152" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>1</v>
       </c>
       <c r="B153" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C153" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>1</v>
       </c>
       <c r="B154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C154" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>1</v>
       </c>
       <c r="B155" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C155" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>1</v>
       </c>
       <c r="B156" t="s">
+        <v>156</v>
+      </c>
+      <c r="C156" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>1</v>
+      </c>
+      <c r="B157" t="s">
         <v>157</v>
-      </c>
-      <c r="C156" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A157">
-        <v>1</v>
-      </c>
-      <c r="B157" t="s">
-        <v>158</v>
       </c>
       <c r="C157" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>1</v>
       </c>
       <c r="B158" t="s">
+        <v>158</v>
+      </c>
+      <c r="C158" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
         <v>159</v>
       </c>
-      <c r="C158" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>1</v>
-      </c>
-      <c r="B159" t="s">
+      <c r="C159" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
         <v>160</v>
-      </c>
-      <c r="C159" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A160">
-        <v>1</v>
-      </c>
-      <c r="B160" t="s">
-        <v>161</v>
       </c>
       <c r="C160" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>1</v>
       </c>
       <c r="B161" t="s">
+        <v>161</v>
+      </c>
+      <c r="C161" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>1</v>
+      </c>
+      <c r="B162" t="s">
         <v>162</v>
-      </c>
-      <c r="C161" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A162">
-        <v>1</v>
-      </c>
-      <c r="B162" t="s">
-        <v>163</v>
       </c>
       <c r="C162" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>1</v>
       </c>
       <c r="B163" t="s">
+        <v>163</v>
+      </c>
+      <c r="C163" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>1</v>
+      </c>
+      <c r="B164" t="s">
         <v>164</v>
-      </c>
-      <c r="C163" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A164">
-        <v>1</v>
-      </c>
-      <c r="B164" t="s">
-        <v>165</v>
       </c>
       <c r="C164" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>1</v>
       </c>
       <c r="B165" t="s">
+        <v>165</v>
+      </c>
+      <c r="C165" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>1</v>
+      </c>
+      <c r="B166" t="s">
         <v>166</v>
-      </c>
-      <c r="C165" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A166">
-        <v>1</v>
-      </c>
-      <c r="B166" t="s">
-        <v>167</v>
       </c>
       <c r="C166" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>1</v>
       </c>
       <c r="B167" t="s">
+        <v>167</v>
+      </c>
+      <c r="C167" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>1</v>
+      </c>
+      <c r="B168" t="s">
         <v>168</v>
-      </c>
-      <c r="C167" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A168">
-        <v>1</v>
-      </c>
-      <c r="B168" t="s">
-        <v>169</v>
       </c>
       <c r="C168" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C169" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>1</v>
       </c>
       <c r="B170" t="s">
+        <v>170</v>
+      </c>
+      <c r="C170" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>1</v>
+      </c>
+      <c r="B171" t="s">
         <v>171</v>
-      </c>
-      <c r="C170" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>1</v>
-      </c>
-      <c r="B171" t="s">
-        <v>172</v>
       </c>
       <c r="C171" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>1</v>
       </c>
       <c r="B172" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C172" s="1">
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>1</v>
       </c>
       <c r="B173" t="s">
+        <v>173</v>
+      </c>
+      <c r="C173" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>1</v>
+      </c>
+      <c r="B174" t="s">
         <v>174</v>
-      </c>
-      <c r="C173" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A174">
-        <v>1</v>
-      </c>
-      <c r="B174" t="s">
-        <v>175</v>
       </c>
       <c r="C174" s="1">
         <v>-0.75</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>1</v>
       </c>
       <c r="B175" t="s">
+        <v>175</v>
+      </c>
+      <c r="C175" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>1</v>
+      </c>
+      <c r="B176" t="s">
         <v>176</v>
       </c>
-      <c r="C175" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A176">
-        <v>1</v>
-      </c>
-      <c r="B176" t="s">
+      <c r="C176" s="1">
+        <v>1</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>1</v>
+      </c>
+      <c r="B177" t="s">
         <v>177</v>
-      </c>
-      <c r="C176" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A177">
-        <v>1</v>
-      </c>
-      <c r="B177" t="s">
-        <v>178</v>
       </c>
       <c r="C177" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>1</v>
       </c>
       <c r="B178" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C178" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>1</v>
       </c>
       <c r="B179" t="s">
+        <v>179</v>
+      </c>
+      <c r="C179" s="1">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>1</v>
+      </c>
+      <c r="B180" t="s">
         <v>180</v>
       </c>
-      <c r="C179" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A180">
-        <v>1</v>
-      </c>
-      <c r="B180" t="s">
+      <c r="C180" s="1">
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>1</v>
+      </c>
+      <c r="B181" t="s">
         <v>181</v>
-      </c>
-      <c r="C180" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A181">
-        <v>1</v>
-      </c>
-      <c r="B181" t="s">
-        <v>182</v>
       </c>
       <c r="C181" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>1</v>
       </c>
       <c r="B182" t="s">
+        <v>182</v>
+      </c>
+      <c r="C182" s="1">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>1</v>
+      </c>
+      <c r="B183" t="s">
         <v>183</v>
-      </c>
-      <c r="C182" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A183">
-        <v>1</v>
-      </c>
-      <c r="B183" t="s">
-        <v>184</v>
       </c>
       <c r="C183" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>1</v>
       </c>
       <c r="B184" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C184" s="1">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>1</v>
       </c>
       <c r="B185" t="s">
+        <v>185</v>
+      </c>
+      <c r="C185" s="1">
+        <v>1</v>
+      </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>1</v>
+      </c>
+      <c r="B186" t="s">
         <v>186</v>
       </c>
-      <c r="C185" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A186">
-        <v>1</v>
-      </c>
-      <c r="B186" t="s">
+      <c r="C186" s="1">
+        <v>1</v>
+      </c>
+      <c r="D186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>1</v>
+      </c>
+      <c r="B187" t="s">
         <v>187</v>
       </c>
-      <c r="C186" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A187">
-        <v>1</v>
-      </c>
-      <c r="B187" t="s">
+      <c r="C187" s="1">
+        <v>1</v>
+      </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>1</v>
+      </c>
+      <c r="B188" t="s">
         <v>188</v>
       </c>
-      <c r="C187" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A188">
-        <v>1</v>
-      </c>
-      <c r="B188" t="s">
+      <c r="C188" s="1">
+        <v>1</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>1</v>
+      </c>
+      <c r="B189" t="s">
         <v>189</v>
       </c>
-      <c r="C188" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A189">
-        <v>1</v>
-      </c>
-      <c r="B189" t="s">
+      <c r="C189" s="1">
+        <v>1</v>
+      </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>1</v>
+      </c>
+      <c r="B190" t="s">
         <v>190</v>
-      </c>
-      <c r="C189" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A190">
-        <v>1</v>
-      </c>
-      <c r="B190" t="s">
-        <v>191</v>
       </c>
       <c r="C190" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>1</v>
       </c>
       <c r="B191" t="s">
+        <v>191</v>
+      </c>
+      <c r="C191" s="1">
+        <v>1</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>1</v>
+      </c>
+      <c r="B192" t="s">
         <v>192</v>
       </c>
-      <c r="C191" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A192">
-        <v>1</v>
-      </c>
-      <c r="B192" t="s">
+      <c r="C192" s="1">
+        <v>1</v>
+      </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>1</v>
+      </c>
+      <c r="B193" t="s">
         <v>193</v>
       </c>
-      <c r="C192" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A193">
-        <v>1</v>
-      </c>
-      <c r="B193" t="s">
+      <c r="C193" s="1">
+        <v>1</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>1</v>
+      </c>
+      <c r="B194" t="s">
         <v>194</v>
       </c>
-      <c r="C193" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A194">
-        <v>1</v>
-      </c>
-      <c r="B194" t="s">
+      <c r="C194" s="1">
+        <v>1</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>1</v>
+      </c>
+      <c r="B195" t="s">
         <v>195</v>
       </c>
-      <c r="C194" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A195">
-        <v>1</v>
-      </c>
-      <c r="B195" t="s">
+      <c r="C195" s="1">
+        <v>1</v>
+      </c>
+      <c r="D195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>1</v>
+      </c>
+      <c r="B196" t="s">
         <v>196</v>
-      </c>
-      <c r="C195" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A196">
-        <v>1</v>
-      </c>
-      <c r="B196" t="s">
-        <v>197</v>
       </c>
       <c r="C196" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>1</v>
       </c>
       <c r="B197" t="s">
+        <v>197</v>
+      </c>
+      <c r="C197" s="1">
+        <v>1</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>1</v>
+      </c>
+      <c r="B198" t="s">
         <v>198</v>
       </c>
-      <c r="C197" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A198">
-        <v>1</v>
-      </c>
-      <c r="B198" t="s">
+      <c r="C198" s="1">
+        <v>1</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>1</v>
+      </c>
+      <c r="B199" t="s">
         <v>199</v>
       </c>
-      <c r="C198" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A199">
-        <v>1</v>
-      </c>
-      <c r="B199" t="s">
+      <c r="C199" s="1">
+        <v>1</v>
+      </c>
+      <c r="D199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>1</v>
+      </c>
+      <c r="B200" t="s">
         <v>200</v>
       </c>
-      <c r="C199" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A200">
-        <v>1</v>
-      </c>
-      <c r="B200" t="s">
+      <c r="C200" s="1">
+        <v>1</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>1</v>
+      </c>
+      <c r="B201" t="s">
         <v>201</v>
       </c>
-      <c r="C200" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A201">
-        <v>1</v>
-      </c>
-      <c r="B201" t="s">
+      <c r="C201" s="1">
+        <v>1</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>1</v>
+      </c>
+      <c r="B202" t="s">
         <v>202</v>
       </c>
-      <c r="C201" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A202">
-        <v>1</v>
-      </c>
-      <c r="B202" t="s">
+      <c r="C202" s="1">
+        <v>1</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>1</v>
+      </c>
+      <c r="B203" t="s">
         <v>203</v>
       </c>
-      <c r="C202" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A203">
-        <v>1</v>
-      </c>
-      <c r="B203" t="s">
+      <c r="C203" s="1">
+        <v>1</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>1</v>
+      </c>
+      <c r="B204" t="s">
         <v>204</v>
-      </c>
-      <c r="C203" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A204">
-        <v>1</v>
-      </c>
-      <c r="B204" t="s">
-        <v>205</v>
       </c>
       <c r="C204" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>1</v>
       </c>
       <c r="B205" t="s">
+        <v>205</v>
+      </c>
+      <c r="C205" s="1">
+        <v>1</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>1</v>
+      </c>
+      <c r="B206" t="s">
         <v>206</v>
       </c>
-      <c r="C205" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A206">
-        <v>1</v>
-      </c>
-      <c r="B206" t="s">
+      <c r="C206" s="1">
+        <v>1</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>1</v>
+      </c>
+      <c r="B207" t="s">
         <v>207</v>
-      </c>
-      <c r="C206" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A207">
-        <v>1</v>
-      </c>
-      <c r="B207" t="s">
-        <v>208</v>
       </c>
       <c r="C207" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>1</v>
       </c>
       <c r="B208" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C208" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>1</v>
       </c>
       <c r="B209" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C209" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>1</v>
       </c>
       <c r="B210" t="s">
+        <v>211</v>
+      </c>
+      <c r="C210" s="1">
+        <v>1</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>1</v>
+      </c>
+      <c r="B211" t="s">
         <v>212</v>
       </c>
-      <c r="C210" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A211">
-        <v>1</v>
-      </c>
-      <c r="B211" t="s">
+      <c r="C211" s="1">
+        <v>1</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>1</v>
+      </c>
+      <c r="B212" t="s">
         <v>213</v>
-      </c>
-      <c r="C211" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A212">
-        <v>1</v>
-      </c>
-      <c r="B212" t="s">
-        <v>214</v>
       </c>
       <c r="C212" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>1</v>
       </c>
       <c r="B213" t="s">
+        <v>214</v>
+      </c>
+      <c r="C213" s="1">
+        <v>1</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>1</v>
+      </c>
+      <c r="B214" t="s">
         <v>215</v>
       </c>
-      <c r="C213" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A214">
-        <v>1</v>
-      </c>
-      <c r="B214" t="s">
+      <c r="C214" s="1">
+        <v>1</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>1</v>
+      </c>
+      <c r="B215" t="s">
         <v>216</v>
       </c>
-      <c r="C214" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A215">
-        <v>1</v>
-      </c>
-      <c r="B215" t="s">
+      <c r="C215" s="1">
+        <v>1</v>
+      </c>
+      <c r="D215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>1</v>
+      </c>
+      <c r="B216" t="s">
         <v>217</v>
       </c>
-      <c r="C215" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A216">
-        <v>1</v>
-      </c>
-      <c r="B216" t="s">
+      <c r="C216" s="1">
+        <v>1</v>
+      </c>
+      <c r="D216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>1</v>
+      </c>
+      <c r="B217" t="s">
         <v>218</v>
       </c>
-      <c r="C216" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A217">
-        <v>1</v>
-      </c>
-      <c r="B217" t="s">
+      <c r="C217" s="1">
+        <v>1</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>1</v>
+      </c>
+      <c r="B218" t="s">
         <v>219</v>
-      </c>
-      <c r="C217" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A218">
-        <v>1</v>
-      </c>
-      <c r="B218" t="s">
-        <v>220</v>
       </c>
       <c r="C218" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>1</v>
       </c>
       <c r="B219" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C219" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>1</v>
       </c>
       <c r="B220" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C220" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>1</v>
       </c>
       <c r="B221" t="s">
+        <v>221</v>
+      </c>
+      <c r="C221" s="1">
+        <v>1</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>1</v>
+      </c>
+      <c r="B222" t="s">
         <v>222</v>
-      </c>
-      <c r="C221" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A222">
-        <v>1</v>
-      </c>
-      <c r="B222" t="s">
-        <v>223</v>
       </c>
       <c r="C222" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>1</v>
       </c>
       <c r="B223" t="s">
+        <v>223</v>
+      </c>
+      <c r="C223" s="1">
+        <v>1</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>1</v>
+      </c>
+      <c r="B224" t="s">
         <v>224</v>
-      </c>
-      <c r="C223" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A224">
-        <v>1</v>
-      </c>
-      <c r="B224" t="s">
-        <v>225</v>
       </c>
       <c r="C224" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>1</v>
       </c>
       <c r="B225" t="s">
+        <v>225</v>
+      </c>
+      <c r="C225" s="1">
+        <v>1</v>
+      </c>
+      <c r="D225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>1</v>
+      </c>
+      <c r="B226" t="s">
         <v>226</v>
-      </c>
-      <c r="C225" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A226">
-        <v>1</v>
-      </c>
-      <c r="B226" t="s">
-        <v>227</v>
       </c>
       <c r="C226" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>1</v>
       </c>
       <c r="B227" t="s">
+        <v>227</v>
+      </c>
+      <c r="C227" s="1">
+        <v>1</v>
+      </c>
+      <c r="D227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>1</v>
+      </c>
+      <c r="B228" t="s">
         <v>228</v>
       </c>
-      <c r="C227" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A228">
-        <v>1</v>
-      </c>
-      <c r="B228" t="s">
+      <c r="C228" s="1">
+        <v>1</v>
+      </c>
+      <c r="D228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>1</v>
+      </c>
+      <c r="B229" t="s">
         <v>229</v>
-      </c>
-      <c r="C228" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A229">
-        <v>1</v>
-      </c>
-      <c r="B229" t="s">
-        <v>230</v>
       </c>
       <c r="C229" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>1</v>
       </c>
       <c r="B230" t="s">
+        <v>230</v>
+      </c>
+      <c r="C230" s="1">
+        <v>1</v>
+      </c>
+      <c r="D230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>1</v>
+      </c>
+      <c r="B231" t="s">
         <v>231</v>
       </c>
-      <c r="C230" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A231">
-        <v>1</v>
-      </c>
-      <c r="B231" t="s">
+      <c r="C231" s="1">
+        <v>1</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>1</v>
+      </c>
+      <c r="B232" t="s">
         <v>232</v>
       </c>
-      <c r="C231" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A232">
-        <v>1</v>
-      </c>
-      <c r="B232" t="s">
+      <c r="C232" s="1">
+        <v>1</v>
+      </c>
+      <c r="D232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>1</v>
+      </c>
+      <c r="B233" t="s">
         <v>233</v>
-      </c>
-      <c r="C232" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A233">
-        <v>1</v>
-      </c>
-      <c r="B233" t="s">
-        <v>234</v>
       </c>
       <c r="C233" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>1</v>
       </c>
       <c r="B234" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C234" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>1</v>
       </c>
       <c r="B235" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C235" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>1</v>
       </c>
       <c r="B236" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C236" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>1</v>
       </c>
       <c r="B237" t="s">
+        <v>237</v>
+      </c>
+      <c r="C237" s="1">
+        <v>1</v>
+      </c>
+      <c r="D237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>1</v>
+      </c>
+      <c r="B238" t="s">
         <v>238</v>
       </c>
-      <c r="C237" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A238">
-        <v>1</v>
-      </c>
-      <c r="B238" t="s">
+      <c r="C238" s="1">
+        <v>1</v>
+      </c>
+      <c r="D238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>1</v>
+      </c>
+      <c r="B239" t="s">
         <v>239</v>
       </c>
-      <c r="C238" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A239">
-        <v>1</v>
-      </c>
-      <c r="B239" t="s">
+      <c r="C239" s="1">
+        <v>1</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>1</v>
+      </c>
+      <c r="B240" t="s">
         <v>240</v>
-      </c>
-      <c r="C239" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A240">
-        <v>1</v>
-      </c>
-      <c r="B240" t="s">
-        <v>241</v>
       </c>
       <c r="C240" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>1</v>
       </c>
       <c r="B241" t="s">
+        <v>241</v>
+      </c>
+      <c r="C241" s="1">
+        <v>1</v>
+      </c>
+      <c r="D241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>1</v>
+      </c>
+      <c r="B242" t="s">
         <v>242</v>
       </c>
-      <c r="C241" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A242">
-        <v>1</v>
-      </c>
-      <c r="B242" t="s">
+      <c r="C242" s="1">
+        <v>1</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>1</v>
+      </c>
+      <c r="B243" t="s">
         <v>243</v>
       </c>
-      <c r="C242" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A243">
-        <v>1</v>
-      </c>
-      <c r="B243" t="s">
+      <c r="C243" s="1">
+        <v>1</v>
+      </c>
+      <c r="D243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>1</v>
+      </c>
+      <c r="B244" t="s">
         <v>244</v>
       </c>
-      <c r="C243" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A244">
-        <v>1</v>
-      </c>
-      <c r="B244" t="s">
+      <c r="C244" s="1">
+        <v>1</v>
+      </c>
+      <c r="D244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>1</v>
+      </c>
+      <c r="B245" t="s">
         <v>245</v>
-      </c>
-      <c r="C244" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A245">
-        <v>1</v>
-      </c>
-      <c r="B245" t="s">
-        <v>246</v>
       </c>
       <c r="C245" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>1</v>
       </c>
       <c r="B246" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C246" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>1</v>
       </c>
       <c r="B247" t="s">
+        <v>247</v>
+      </c>
+      <c r="C247" s="1">
+        <v>1</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>1</v>
+      </c>
+      <c r="B248" t="s">
         <v>248</v>
       </c>
-      <c r="C247" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A248">
-        <v>1</v>
-      </c>
-      <c r="B248" t="s">
+      <c r="C248" s="1">
+        <v>1</v>
+      </c>
+      <c r="D248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>1</v>
+      </c>
+      <c r="B249" t="s">
         <v>249</v>
       </c>
-      <c r="C248" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A249">
-        <v>1</v>
-      </c>
-      <c r="B249" t="s">
+      <c r="C249" s="1">
+        <v>1</v>
+      </c>
+      <c r="D249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>1</v>
+      </c>
+      <c r="B250" t="s">
         <v>250</v>
-      </c>
-      <c r="C249" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A250">
-        <v>1</v>
-      </c>
-      <c r="B250" t="s">
-        <v>251</v>
       </c>
       <c r="C250" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>1</v>
       </c>
       <c r="B251" t="s">
+        <v>251</v>
+      </c>
+      <c r="C251" s="1">
+        <v>1</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>1</v>
+      </c>
+      <c r="B252" t="s">
         <v>252</v>
       </c>
-      <c r="C251" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A252">
-        <v>1</v>
-      </c>
-      <c r="B252" t="s">
+      <c r="C252" s="1">
+        <v>1</v>
+      </c>
+      <c r="D252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>1</v>
+      </c>
+      <c r="B253" t="s">
         <v>253</v>
       </c>
-      <c r="C252" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A253">
-        <v>1</v>
-      </c>
-      <c r="B253" t="s">
+      <c r="C253" s="1">
+        <v>1</v>
+      </c>
+      <c r="D253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>1</v>
+      </c>
+      <c r="B254" t="s">
         <v>254</v>
       </c>
-      <c r="C253" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A254">
-        <v>1</v>
-      </c>
-      <c r="B254" t="s">
+      <c r="C254" s="1">
+        <v>1</v>
+      </c>
+      <c r="D254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>1</v>
+      </c>
+      <c r="B255" t="s">
         <v>255</v>
       </c>
-      <c r="C254" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A255">
-        <v>1</v>
-      </c>
-      <c r="B255" t="s">
+      <c r="C255" s="1">
+        <v>1</v>
+      </c>
+      <c r="D255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>1</v>
+      </c>
+      <c r="B256" t="s">
         <v>256</v>
       </c>
-      <c r="C255" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A256">
-        <v>1</v>
-      </c>
-      <c r="B256" t="s">
+      <c r="C256" s="1">
+        <v>1</v>
+      </c>
+      <c r="D256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>1</v>
+      </c>
+      <c r="B257" t="s">
         <v>257</v>
       </c>
-      <c r="C256" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A257">
-        <v>1</v>
-      </c>
-      <c r="B257" t="s">
+      <c r="C257" s="1">
+        <v>1</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>1</v>
+      </c>
+      <c r="B258" t="s">
         <v>258</v>
       </c>
-      <c r="C257" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A258">
-        <v>1</v>
-      </c>
-      <c r="B258" t="s">
+      <c r="C258" s="1">
+        <v>1</v>
+      </c>
+      <c r="D258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>1</v>
+      </c>
+      <c r="B259" t="s">
         <v>259</v>
       </c>
-      <c r="C258" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A259">
-        <v>1</v>
-      </c>
-      <c r="B259" t="s">
+      <c r="C259" s="1">
+        <v>1</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>1</v>
+      </c>
+      <c r="B260" t="s">
         <v>260</v>
       </c>
-      <c r="C259" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A260">
-        <v>1</v>
-      </c>
-      <c r="B260" t="s">
+      <c r="C260" s="1">
+        <v>1</v>
+      </c>
+      <c r="D260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>1</v>
+      </c>
+      <c r="B261" t="s">
         <v>261</v>
       </c>
-      <c r="C260" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A261">
-        <v>1</v>
-      </c>
-      <c r="B261" t="s">
+      <c r="C261" s="1">
+        <v>1</v>
+      </c>
+      <c r="D261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>1</v>
+      </c>
+      <c r="B262" t="s">
         <v>262</v>
       </c>
-      <c r="C261" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A262">
-        <v>1</v>
-      </c>
-      <c r="B262" t="s">
+      <c r="C262" s="1">
+        <v>1</v>
+      </c>
+      <c r="D262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>1</v>
+      </c>
+      <c r="B263" t="s">
         <v>263</v>
       </c>
-      <c r="C262" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A263">
-        <v>1</v>
-      </c>
-      <c r="B263" t="s">
+      <c r="C263" s="1">
+        <v>1</v>
+      </c>
+      <c r="D263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>1</v>
+      </c>
+      <c r="B264" t="s">
         <v>264</v>
       </c>
-      <c r="C263" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A264">
-        <v>1</v>
-      </c>
-      <c r="B264" t="s">
+      <c r="C264" s="1">
+        <v>1</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>1</v>
+      </c>
+      <c r="B265" t="s">
         <v>265</v>
-      </c>
-      <c r="C264" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A265">
-        <v>1</v>
-      </c>
-      <c r="B265" t="s">
-        <v>266</v>
       </c>
       <c r="C265" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>1</v>
       </c>
       <c r="B266" t="s">
+        <v>266</v>
+      </c>
+      <c r="C266" s="1">
+        <v>1</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>1</v>
+      </c>
+      <c r="B267" t="s">
         <v>267</v>
-      </c>
-      <c r="C266" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A267">
-        <v>1</v>
-      </c>
-      <c r="B267" t="s">
-        <v>268</v>
       </c>
       <c r="C267" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>1</v>
       </c>
       <c r="B268" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C268" s="1">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>1</v>
       </c>
       <c r="B269" t="s">
+        <v>269</v>
+      </c>
+      <c r="C269" s="1">
+        <v>1</v>
+      </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>1</v>
+      </c>
+      <c r="B270" t="s">
         <v>270</v>
       </c>
-      <c r="C269" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A270">
-        <v>1</v>
-      </c>
-      <c r="B270" t="s">
+      <c r="C270" s="1">
+        <v>1</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>1</v>
+      </c>
+      <c r="B271" t="s">
         <v>271</v>
       </c>
-      <c r="C270" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A271">
-        <v>1</v>
-      </c>
-      <c r="B271" t="s">
+      <c r="C271" s="1">
+        <v>1</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>1</v>
+      </c>
+      <c r="B272" t="s">
         <v>272</v>
-      </c>
-      <c r="C271" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A272">
-        <v>1</v>
-      </c>
-      <c r="B272" t="s">
-        <v>273</v>
       </c>
       <c r="C272" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>1</v>
       </c>
       <c r="B273" t="s">
+        <v>273</v>
+      </c>
+      <c r="C273" s="1">
+        <v>1</v>
+      </c>
+      <c r="D273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>1</v>
+      </c>
+      <c r="B274" t="s">
         <v>274</v>
       </c>
-      <c r="C273" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A274">
-        <v>1</v>
-      </c>
-      <c r="B274" t="s">
+      <c r="C274" s="1">
+        <v>1</v>
+      </c>
+      <c r="D274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>1</v>
+      </c>
+      <c r="B275" t="s">
         <v>275</v>
       </c>
-      <c r="C274" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A275">
-        <v>1</v>
-      </c>
-      <c r="B275" t="s">
+      <c r="C275" s="1">
+        <v>1</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>1</v>
+      </c>
+      <c r="B276" t="s">
         <v>276</v>
       </c>
-      <c r="C275" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A276">
-        <v>1</v>
-      </c>
-      <c r="B276" t="s">
+      <c r="C276" s="1">
+        <v>1</v>
+      </c>
+      <c r="D276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>1</v>
+      </c>
+      <c r="B277" t="s">
         <v>277</v>
       </c>
-      <c r="C276" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A277">
-        <v>1</v>
-      </c>
-      <c r="B277" t="s">
+      <c r="C277" s="1">
+        <v>1</v>
+      </c>
+      <c r="D277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>1</v>
+      </c>
+      <c r="B278" t="s">
         <v>278</v>
       </c>
-      <c r="C277" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A278">
-        <v>1</v>
-      </c>
-      <c r="B278" t="s">
+      <c r="C278" s="1">
+        <v>1</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>1</v>
+      </c>
+      <c r="B279" t="s">
         <v>279</v>
-      </c>
-      <c r="C278" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A279">
-        <v>1</v>
-      </c>
-      <c r="B279" t="s">
-        <v>280</v>
       </c>
       <c r="C279" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>1</v>
       </c>
       <c r="B280" t="s">
+        <v>280</v>
+      </c>
+      <c r="C280" s="1">
+        <v>1</v>
+      </c>
+      <c r="D280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>1</v>
+      </c>
+      <c r="B281" t="s">
         <v>281</v>
       </c>
-      <c r="C280" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A281">
-        <v>1</v>
-      </c>
-      <c r="B281" t="s">
+      <c r="C281" s="1">
+        <v>1</v>
+      </c>
+      <c r="D281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>1</v>
+      </c>
+      <c r="B282" t="s">
         <v>282</v>
-      </c>
-      <c r="C281" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A282">
-        <v>1</v>
-      </c>
-      <c r="B282" t="s">
-        <v>283</v>
       </c>
       <c r="C282" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>1</v>
       </c>
       <c r="B283" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C283" s="1">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>1</v>
       </c>
       <c r="B284" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C284" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>1</v>
       </c>
       <c r="B285" t="s">
+        <v>285</v>
+      </c>
+      <c r="C285" s="1">
+        <v>1</v>
+      </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>1</v>
+      </c>
+      <c r="B286" t="s">
         <v>286</v>
-      </c>
-      <c r="C285" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A286">
-        <v>1</v>
-      </c>
-      <c r="B286" t="s">
-        <v>287</v>
       </c>
       <c r="C286" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>1</v>
       </c>
       <c r="B287" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C287" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>1</v>
       </c>
       <c r="B288" t="s">
+        <v>288</v>
+      </c>
+      <c r="C288" s="1">
+        <v>1</v>
+      </c>
+      <c r="D288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>1</v>
+      </c>
+      <c r="B289" t="s">
         <v>289</v>
       </c>
-      <c r="C288" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A289">
-        <v>1</v>
-      </c>
-      <c r="B289" t="s">
+      <c r="C289" s="1">
+        <v>1</v>
+      </c>
+      <c r="D289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>1</v>
+      </c>
+      <c r="B290" t="s">
         <v>290</v>
       </c>
-      <c r="C289" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A290">
-        <v>1</v>
-      </c>
-      <c r="B290" t="s">
+      <c r="C290" s="1">
+        <v>1</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>1</v>
+      </c>
+      <c r="B291" t="s">
         <v>291</v>
       </c>
-      <c r="C290" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A291">
-        <v>1</v>
-      </c>
-      <c r="B291" t="s">
+      <c r="C291" s="1">
+        <v>1</v>
+      </c>
+      <c r="D291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>1</v>
+      </c>
+      <c r="B292" t="s">
         <v>292</v>
-      </c>
-      <c r="C291" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A292">
-        <v>1</v>
-      </c>
-      <c r="B292" t="s">
-        <v>293</v>
       </c>
       <c r="C292" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>1</v>
       </c>
       <c r="B293" t="s">
+        <v>293</v>
+      </c>
+      <c r="C293" s="1">
+        <v>1</v>
+      </c>
+      <c r="D293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>1</v>
+      </c>
+      <c r="B294" t="s">
         <v>294</v>
-      </c>
-      <c r="C293" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A294">
-        <v>1</v>
-      </c>
-      <c r="B294" t="s">
-        <v>295</v>
       </c>
       <c r="C294" s="1">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>1</v>
       </c>
       <c r="B295" t="s">
+        <v>295</v>
+      </c>
+      <c r="C295" s="1">
+        <v>1</v>
+      </c>
+      <c r="D295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>1</v>
+      </c>
+      <c r="B296" t="s">
         <v>296</v>
-      </c>
-      <c r="C295" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A296">
-        <v>1</v>
-      </c>
-      <c r="B296" t="s">
-        <v>297</v>
       </c>
       <c r="C296" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>1</v>
       </c>
       <c r="B297" t="s">
+        <v>297</v>
+      </c>
+      <c r="C297" s="1">
+        <v>1</v>
+      </c>
+      <c r="D297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>1</v>
+      </c>
+      <c r="B298" t="s">
         <v>298</v>
-      </c>
-      <c r="C297" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A298">
-        <v>1</v>
-      </c>
-      <c r="B298" t="s">
-        <v>299</v>
       </c>
       <c r="C298" s="1">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>1</v>
       </c>
       <c r="B299" t="s">
+        <v>299</v>
+      </c>
+      <c r="C299" s="1">
+        <v>1</v>
+      </c>
+      <c r="D299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>1</v>
+      </c>
+      <c r="B300" t="s">
         <v>300</v>
       </c>
-      <c r="C299" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A300">
-        <v>1</v>
-      </c>
-      <c r="B300" t="s">
+      <c r="C300" s="1">
+        <v>1</v>
+      </c>
+      <c r="D300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>1</v>
+      </c>
+      <c r="B301" t="s">
         <v>301</v>
-      </c>
-      <c r="C300" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A301">
-        <v>1</v>
-      </c>
-      <c r="B301" t="s">
-        <v>302</v>
       </c>
       <c r="C301" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>1</v>
       </c>
       <c r="B302" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C302" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>1</v>
       </c>
       <c r="B303" t="s">
+        <v>303</v>
+      </c>
+      <c r="C303" s="1">
+        <v>1</v>
+      </c>
+      <c r="D303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>1</v>
+      </c>
+      <c r="B304" t="s">
         <v>304</v>
       </c>
-      <c r="C303" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A304">
-        <v>1</v>
-      </c>
-      <c r="B304" t="s">
+      <c r="C304" s="1">
+        <v>1</v>
+      </c>
+      <c r="D304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>1</v>
+      </c>
+      <c r="B305" t="s">
         <v>305</v>
       </c>
-      <c r="C304" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A305">
-        <v>1</v>
-      </c>
-      <c r="B305" t="s">
+      <c r="C305" s="1">
+        <v>1</v>
+      </c>
+      <c r="D305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>1</v>
+      </c>
+      <c r="B306" t="s">
         <v>306</v>
       </c>
-      <c r="C305" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A306">
-        <v>1</v>
-      </c>
-      <c r="B306" t="s">
+      <c r="C306" s="1">
+        <v>1</v>
+      </c>
+      <c r="D306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>1</v>
+      </c>
+      <c r="B307" t="s">
         <v>307</v>
-      </c>
-      <c r="C306" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A307">
-        <v>1</v>
-      </c>
-      <c r="B307" t="s">
-        <v>308</v>
       </c>
       <c r="C307" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>1</v>
       </c>
       <c r="B308" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C308" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>1</v>
       </c>
       <c r="B309" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C309" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>1</v>
       </c>
       <c r="B310" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C310" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>1</v>
       </c>
       <c r="B311" t="s">
+        <v>311</v>
+      </c>
+      <c r="C311" s="1">
+        <v>1</v>
+      </c>
+      <c r="D311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>1</v>
+      </c>
+      <c r="B312" t="s">
         <v>312</v>
       </c>
-      <c r="C311" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A312">
-        <v>1</v>
-      </c>
-      <c r="B312" t="s">
+      <c r="C312" s="1">
+        <v>1</v>
+      </c>
+      <c r="D312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>1</v>
+      </c>
+      <c r="B313" t="s">
         <v>313</v>
-      </c>
-      <c r="C312" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A313">
-        <v>1</v>
-      </c>
-      <c r="B313" t="s">
-        <v>314</v>
       </c>
       <c r="C313" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>1</v>
       </c>
       <c r="B314" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C314" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>1</v>
       </c>
       <c r="B315" t="s">
+        <v>315</v>
+      </c>
+      <c r="C315" s="1">
+        <v>1</v>
+      </c>
+      <c r="D315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>1</v>
+      </c>
+      <c r="B316" t="s">
         <v>316</v>
       </c>
-      <c r="C315" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A316">
-        <v>1</v>
-      </c>
-      <c r="B316" t="s">
+      <c r="C316" s="1">
+        <v>1</v>
+      </c>
+      <c r="D316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>1</v>
+      </c>
+      <c r="B317" t="s">
         <v>317</v>
       </c>
-      <c r="C316" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A317">
-        <v>1</v>
-      </c>
-      <c r="B317" t="s">
+      <c r="C317" s="1">
+        <v>1</v>
+      </c>
+      <c r="D317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>1</v>
+      </c>
+      <c r="B318" t="s">
         <v>318</v>
-      </c>
-      <c r="C317" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A318">
-        <v>1</v>
-      </c>
-      <c r="B318" t="s">
-        <v>319</v>
       </c>
       <c r="C318" s="1">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>1</v>
       </c>
       <c r="B319" t="s">
+        <v>319</v>
+      </c>
+      <c r="C319" s="1">
+        <v>1</v>
+      </c>
+      <c r="D319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>1</v>
+      </c>
+      <c r="B320" t="s">
         <v>320</v>
-      </c>
-      <c r="C319" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A320">
-        <v>1</v>
-      </c>
-      <c r="B320" t="s">
-        <v>321</v>
       </c>
       <c r="C320" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>1</v>
       </c>
       <c r="B321" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C321" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
       <c r="B322" t="s">
+        <v>322</v>
+      </c>
+      <c r="C322" s="1">
+        <v>1</v>
+      </c>
+      <c r="D322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>1</v>
+      </c>
+      <c r="B323" t="s">
         <v>323</v>
       </c>
-      <c r="C322" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A323">
-        <v>1</v>
-      </c>
-      <c r="B323" t="s">
+      <c r="C323" s="1">
+        <v>1</v>
+      </c>
+      <c r="D323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>1</v>
+      </c>
+      <c r="B324" t="s">
         <v>324</v>
-      </c>
-      <c r="C323" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A324">
-        <v>1</v>
-      </c>
-      <c r="B324" t="s">
-        <v>325</v>
       </c>
       <c r="C324" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>1</v>
       </c>
       <c r="B325" t="s">
+        <v>325</v>
+      </c>
+      <c r="C325" s="1">
+        <v>1</v>
+      </c>
+      <c r="D325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>1</v>
+      </c>
+      <c r="B326" t="s">
         <v>326</v>
       </c>
-      <c r="C325" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A326">
-        <v>1</v>
-      </c>
-      <c r="B326" t="s">
+      <c r="C326" s="1">
+        <v>1</v>
+      </c>
+      <c r="D326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>1</v>
+      </c>
+      <c r="B327" t="s">
         <v>327</v>
-      </c>
-      <c r="C326" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A327">
-        <v>1</v>
-      </c>
-      <c r="B327" t="s">
-        <v>328</v>
       </c>
       <c r="C327" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>1</v>
       </c>
       <c r="B328" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C328" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>1</v>
       </c>
       <c r="B329" t="s">
+        <v>329</v>
+      </c>
+      <c r="C329" s="1">
+        <v>1</v>
+      </c>
+      <c r="D329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>1</v>
+      </c>
+      <c r="B330" t="s">
         <v>330</v>
-      </c>
-      <c r="C329" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A330">
-        <v>1</v>
-      </c>
-      <c r="B330" t="s">
-        <v>331</v>
       </c>
       <c r="C330" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>1</v>
       </c>
       <c r="B331" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C331" s="1">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>1</v>
       </c>
       <c r="B332" t="s">
+        <v>332</v>
+      </c>
+      <c r="C332" s="1">
+        <v>1</v>
+      </c>
+      <c r="D332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>1</v>
+      </c>
+      <c r="B333" t="s">
         <v>333</v>
       </c>
-      <c r="C332" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A333">
-        <v>1</v>
-      </c>
-      <c r="B333" t="s">
+      <c r="C333" s="1">
+        <v>1</v>
+      </c>
+      <c r="D333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>1</v>
+      </c>
+      <c r="B334" t="s">
         <v>334</v>
       </c>
-      <c r="C333" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A334">
-        <v>1</v>
-      </c>
-      <c r="B334" t="s">
+      <c r="C334" s="1">
+        <v>1</v>
+      </c>
+      <c r="D334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>1</v>
+      </c>
+      <c r="B335" t="s">
         <v>335</v>
       </c>
-      <c r="C334" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A335">
-        <v>1</v>
-      </c>
-      <c r="B335" t="s">
+      <c r="C335" s="1">
+        <v>1</v>
+      </c>
+      <c r="D335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>1</v>
+      </c>
+      <c r="B336" t="s">
         <v>336</v>
       </c>
-      <c r="C335" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A336">
-        <v>1</v>
-      </c>
-      <c r="B336" t="s">
+      <c r="C336" s="1">
+        <v>1</v>
+      </c>
+      <c r="D336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>1</v>
+      </c>
+      <c r="B337" t="s">
         <v>337</v>
       </c>
-      <c r="C336" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A337">
-        <v>1</v>
-      </c>
-      <c r="B337" t="s">
+      <c r="C337" s="1">
+        <v>1</v>
+      </c>
+      <c r="D337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>1</v>
+      </c>
+      <c r="B338" t="s">
         <v>338</v>
       </c>
-      <c r="C337" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A338">
-        <v>1</v>
-      </c>
-      <c r="B338" t="s">
+      <c r="C338" s="1">
+        <v>1</v>
+      </c>
+      <c r="D338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>1</v>
+      </c>
+      <c r="B339" t="s">
         <v>339</v>
       </c>
-      <c r="C338" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A339">
-        <v>1</v>
-      </c>
-      <c r="B339" t="s">
+      <c r="C339" s="1">
+        <v>1</v>
+      </c>
+      <c r="D339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>1</v>
+      </c>
+      <c r="B340" t="s">
         <v>340</v>
-      </c>
-      <c r="C339" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A340">
-        <v>1</v>
-      </c>
-      <c r="B340" t="s">
-        <v>341</v>
       </c>
       <c r="C340" s="1">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>1</v>
       </c>
       <c r="B341" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C341" s="1">
+        <v>1</v>
+      </c>
+      <c r="D341">
         <v>1</v>
       </c>
     </row>
